--- a/report/downloads/reports/网点变化对比报告_20260601_vs_20260608.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260601_vs_20260608.xlsx
@@ -11518,7 +11518,7 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉江夏永旺销售中心</t>
+          <t>小鹏汽车武汉江宸龙湖天街销售中心</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
@@ -11533,12 +11533,12 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>湖北省武汉市江夏区文化大道199号永旺梦乐城1F-1062-2</t>
+          <t>湖北省武汉市江汉区青年路518号江宸龙湖天街负一楼小鹏汽车体验中心</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>连续在档 5 期；本期存在高相似店名「小鹏汽车武汉经开永旺销售中心」（疑似改名/合并，非真实关店）</t>
+          <t>连续在档 5 期</t>
         </is>
       </c>
     </row>
@@ -11550,7 +11550,7 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉江宸龙湖天街销售中心</t>
+          <t>小鹏汽车武汉江夏永旺销售中心</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
@@ -11565,12 +11565,12 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>湖北省武汉市江汉区青年路518号江宸龙湖天街负一楼小鹏汽车体验中心</t>
+          <t>湖北省武汉市江夏区文化大道199号永旺梦乐城1F-1062-2</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>连续在档 5 期</t>
+          <t>连续在档 5 期；本期存在高相似店名「小鹏汽车武汉经开永旺销售中心」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -12446,7 +12446,7 @@
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>华为智能生活馆•西宁海湖万达</t>
+          <t>华为智能生活馆•西宁王府井百货</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
@@ -12461,7 +12461,7 @@
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>青海省西宁市城西区海湖新区西关大街海湖万达广场2号门左侧</t>
+          <t>青海省西宁市城中区西大街王府井百货B馆</t>
         </is>
       </c>
       <c r="F50" s="3" t="inlineStr">
@@ -12478,7 +12478,7 @@
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>华为智能生活馆•西宁城东吾悦</t>
+          <t>华为智能生活馆•西宁海湖万达</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
@@ -12493,7 +12493,7 @@
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>青海省西宁市城东区八一路与民和路交叉口东南西宁城东吾悦广场</t>
+          <t>青海省西宁市城西区海湖新区西关大街海湖万达广场2号门左侧</t>
         </is>
       </c>
       <c r="F51" s="3" t="inlineStr">
@@ -12510,7 +12510,7 @@
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>华为智能生活馆•西宁王府井百货</t>
+          <t>华为智能生活馆•西宁城东吾悦</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
@@ -12525,7 +12525,7 @@
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>青海省西宁市城中区西大街王府井百货B馆</t>
+          <t>青海省西宁市城东区八一路与民和路交叉口东南西宁城东吾悦广场</t>
         </is>
       </c>
       <c r="F52" s="3" t="inlineStr">
@@ -12596,17 +12596,17 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>小鹏汽车潍坊潍州路销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>小鹏汽车潍坊潍州路销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12616,7 +12616,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>佛山市禅城区南庄镇醒群社村工业区5号 → 广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号</t>
+          <t>山东省潍坊市奎文区潍州路2800号 → 潍坊市奎文区金宝乐园南100米路西</t>
         </is>
       </c>
     </row>
@@ -12628,17 +12628,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车乐山天牛汽车城销售服务中心</t>
+          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车乐山天牛汽车城销售服务中心</t>
+          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12648,7 +12648,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>四川省乐山市市中区龙游路北段518号 → 四川省乐山市市中区龙游路北段518号1幢</t>
+          <t>繁华大道29华天大厦向东20米3号整栋标准厂房 → 安徽省合肥市包河经济开发区繁华大道29华天大厦向东20米3号整栋标准厂房</t>
         </is>
       </c>
     </row>
@@ -12660,17 +12660,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小鹏汽车福州海盛汽车城交付中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小鹏汽车福州海盛汽车城交付中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12680,14 +12680,14 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
+          <t>福州市闽侯县荆溪镇永丰村洪甘路189号海盛汽车城 → 荆溪镇永丰村杜坞42号海盛汽车城A区5栋1层小鹏福州海盛交付中心</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
@@ -12697,12 +12697,12 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>小鹏汽车北京五方天雅销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>小鹏汽车北京五方天雅销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12712,7 +12712,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>龙跃街9号院 顺义区马坡聚源工业园 101317 → 新东路幸福二村40号楼 朝阳区 100027</t>
+          <t>北京市朝阳区王四营乡五方天雅B区B1-03 → 北京市朝阳区五方桥西南侧五方天雅市场内B区B1-03号</t>
         </is>
       </c>
     </row>
@@ -12756,17 +12756,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>小鹏汽车海口南海大道销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>小鹏汽车海口南海大道销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12776,7 +12776,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>河北省张家口市经济技术开发区张宣公路西侧白云街1号 → 河北省张家口市经济技术开发区白云街1号万国汽配城后</t>
+          <t>海南省海口市龙华区南海大道115号福德汽车城小鹏汽车 → 海南省海口市龙华区南海大道115号</t>
         </is>
       </c>
     </row>
@@ -12788,17 +12788,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津北辰双江道销售服务中心</t>
+          <t>小鹏汽车重庆万象城销售中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津北辰双江道销售服务中心</t>
+          <t>小鹏汽车重庆万象城销售中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12808,14 +12808,14 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>天津市北辰区双街镇庞大汽贸园原五菱宝骏店展厅 → 天津市北辰区双街镇庞大汽贸园原五菱骏宝店展厅</t>
+          <t>重庆市九龙坡区万象城北区 → 重庆市九龙坡区万象城北区3号门NL132</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
@@ -12825,12 +12825,12 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕头龙湖销售服务中心</t>
+          <t>广州市锦龙汽车发展有限公司</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕头龙湖销售服务中心</t>
+          <t>广州市锦龙汽车发展有限公司</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12840,29 +12840,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>广东省汕头市龙湖区汕汾路与淮河路交界处北侧 → 汕头市龙湖区汕汾路与淮河路交界处北侧之一（东侧）</t>
+          <t>广东省广州市天河区广东省广州市天河区黄村街道奥体路55号(奥林匹克体育中心东门对面) → 广东省广州市天河区奥体南路5号</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>广州市锦龙汽车发展有限公司</t>
+          <t>小鹏汽车文山国际汽车城销售中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>广州市锦龙汽车发展有限公司</t>
+          <t>小鹏汽车文山国际汽车城销售中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12872,29 +12872,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>广东省广州市天河区广东省广州市天河区黄村街道奥体路55号(奥林匹克体育中心东门对面) → 广东省广州市天河区奥体南路5号</t>
+          <t>云南省文山壮族苗族自治州文山市腾龙北路世纪名苑二期 → 云南省文山壮族苗族自治州文山市腾龙北路世纪名苑B期第28-31号商铺</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
+          <t>上海德辰汽车销售有限公司</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
+          <t>上海德辰汽车销售有限公司</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12904,7 +12904,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>繁华大道29华天大厦向东20米3号整栋标准厂房 → 安徽省合肥市包河经济开发区繁华大道29华天大厦向东20米3号整栋标准厂房</t>
+          <t>上海市闵行区颛兴东路1280弄3号(都会路口) → 上海市闵行区莲花南路2333号</t>
         </is>
       </c>
     </row>
@@ -12916,17 +12916,17 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州海盛汽车城交付中心</t>
+          <t>小鹏汽车天津北辰双江道销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州海盛汽车城交付中心</t>
+          <t>小鹏汽车天津北辰双江道销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12936,7 +12936,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>福州市闽侯县荆溪镇永丰村洪甘路189号海盛汽车城 → 荆溪镇永丰村杜坞42号海盛汽车城A区5栋1层小鹏福州海盛交付中心</t>
+          <t>天津市北辰区双街镇庞大汽贸园原五菱宝骏店展厅 → 天津市北辰区双街镇庞大汽贸园原五菱骏宝店展厅</t>
         </is>
       </c>
     </row>
@@ -12948,17 +12948,17 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京五方天雅销售服务中心</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京五方天雅销售服务中心</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12968,7 +12968,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>北京市朝阳区王四营乡五方天雅B区B1-03 → 北京市朝阳区五方桥西南侧五方天雅市场内B区B1-03号</t>
+          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
         </is>
       </c>
     </row>
@@ -12980,17 +12980,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -13000,7 +13000,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区四流南路22号-8幢展厅 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心</t>
+          <t>四川省遂宁市遂宁高新区物流港物流大道858-888号 → 四川省遂宁市遂宁高新区物流港主干道B南侧858-888号</t>
         </is>
       </c>
     </row>
@@ -13012,17 +13012,17 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆万象城销售中心</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆万象城销售中心</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -13032,29 +13032,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>重庆市九龙坡区万象城北区 → 重庆市九龙坡区万象城北区3号门NL132</t>
+          <t>河北省张家口市经济技术开发区张宣公路西侧白云街1号 → 河北省张家口市经济技术开发区白云街1号万国汽配城后</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（东吴银泰）</t>
+          <t>小鹏汽车乐山天牛汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（东吴银泰）</t>
+          <t>小鹏汽车乐山天牛汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -13064,7 +13064,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>浙江省湖州市吴兴区劳动路518号湖州东吴银泰城1F层【1001-A,1001-B,1002、1-39】号 → 湖州市吴兴区劳动路518号湖州东吴银泰城1F层C馆（1001-A,1001-B,1002-C) 华为授权体验店</t>
+          <t>四川省乐山市市中区龙游路北段518号 → 四川省乐山市市中区龙游路北段518号1幢</t>
         </is>
       </c>
     </row>
@@ -13076,17 +13076,17 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车文山国际汽车城销售中心</t>
+          <t>小鹏汽车深圳福保销售服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车文山国际汽车城销售中心</t>
+          <t>小鹏汽车深圳福保销售服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13096,29 +13096,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>云南省文山壮族苗族自治州文山市腾龙北路世纪名苑二期 → 云南省文山壮族苗族自治州文山市腾龙北路世纪名苑B期第28-31号商铺</t>
+          <t>深圳市福田保税区蓝花道6号诚联物流大厦1层 → 广东省深圳市福田区蓝花道6号城联物流大厦一层</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
+          <t>昆明经开特斯拉中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
+          <t>昆明经开特斯拉中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13128,29 +13128,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>四川省遂宁市遂宁高新区物流港物流大道858-888号 → 四川省遂宁市遂宁高新区物流港主干道B南侧858-888号</t>
+          <t>云南省昆明市自由贸易试验区昆明片区经开区出口加工区A6-1-2号（宝泽路41号）2栋 → 云南省昆明市经济开发区宝泽路41号2栋</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>昆明经开特斯拉中心</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>昆明经开特斯拉中心</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13160,7 +13160,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>云南省昆明市自由贸易试验区昆明片区经开区出口加工区A6-1-2号（宝泽路41号）2栋 → 云南省昆明市经济开发区宝泽路41号2栋</t>
+          <t>佛山市禅城区南庄镇醒群社村工业区5号 → 广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号</t>
         </is>
       </c>
     </row>
@@ -13172,17 +13172,17 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>小鹏汽车汕头龙湖销售服务中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>小鹏汽车汕头龙湖销售服务中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13192,29 +13192,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅 → 新疆伊宁市巴彦岱城投汽车产业园</t>
+          <t>广东省汕头市龙湖区汕汾路与淮河路交界处北侧 → 汕头市龙湖区汕汾路与淮河路交界处北侧之一（东侧）</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳福保销售服务中心</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳福保销售服务中心</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13224,7 +13224,7 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>深圳市福田保税区蓝花道6号诚联物流大厦1层 → 广东省深圳市福田区蓝花道6号城联物流大厦一层</t>
+          <t>龙跃街9号院 顺义区马坡聚源工业园 101317 → 新东路幸福二村40号楼 朝阳区 100027</t>
         </is>
       </c>
     </row>
@@ -13236,17 +13236,17 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊潍州路销售服务中心</t>
+          <t>小鹏汽车广州龙溪大道销售服务中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊潍州路销售服务中心</t>
+          <t>小鹏汽车广州龙溪大道销售服务中心</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13256,7 +13256,7 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>山东省潍坊市奎文区潍州路2800号 → 潍坊市奎文区金宝乐园南100米路西</t>
+          <t>广东省广州市荔湾区龙溪大道488号场内自编号为86号 → 广东省广州市荔湾区龙溪大道488号金马汽车交易城小鹏汽车</t>
         </is>
       </c>
     </row>
@@ -13268,17 +13268,17 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州龙溪大道销售服务中心</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州龙溪大道销售服务中心</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13288,29 +13288,29 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>广东省广州市荔湾区龙溪大道488号场内自编号为86号 → 广东省广州市荔湾区龙溪大道488号金马汽车交易城小鹏汽车</t>
+          <t>新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅 → 新疆伊宁市巴彦岱城投汽车产业园</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>上海德辰汽车销售有限公司</t>
+          <t>华为授权体验店（东吴银泰）</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>上海德辰汽车销售有限公司</t>
+          <t>华为授权体验店（东吴银泰）</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13320,7 +13320,7 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>上海市闵行区颛兴东路1280弄3号(都会路口) → 上海市闵行区莲花南路2333号</t>
+          <t>浙江省湖州市吴兴区劳动路518号湖州东吴银泰城1F层【1001-A,1001-B,1002、1-39】号 → 湖州市吴兴区劳动路518号湖州东吴银泰城1F层C馆（1001-A,1001-B,1002-C) 华为授权体验店</t>
         </is>
       </c>
     </row>
@@ -13332,17 +13332,17 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海口南海大道销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海口南海大道销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13352,7 +13352,7 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>海南省海口市龙华区南海大道115号福德汽车城小鹏汽车 → 海南省海口市龙华区南海大道115号</t>
+          <t>青岛市市北区四流南路22号-8幢展厅 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心</t>
         </is>
       </c>
     </row>
@@ -13551,22 +13551,22 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>宾利北京亦庄</t>
+          <t>小鹏汽车上海临港万达广场销售中心</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>宾利北京五棵松（新）</t>
+          <t>小鹏汽车上海临港万达销售展厅</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -13583,22 +13583,22 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海临港万达广场销售中心</t>
+          <t>宾利北京亦庄</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海临港万达销售展厅</t>
+          <t>宾利北京五棵松（新）</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260601_vs_20260608.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260601_vs_20260608.xlsx
@@ -11518,7 +11518,7 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉江宸龙湖天街销售中心</t>
+          <t>小鹏汽车武汉江夏永旺销售中心</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
@@ -11533,12 +11533,12 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>湖北省武汉市江汉区青年路518号江宸龙湖天街负一楼小鹏汽车体验中心</t>
+          <t>湖北省武汉市江夏区文化大道199号永旺梦乐城1F-1062-2</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>连续在档 5 期</t>
+          <t>连续在档 5 期；本期存在高相似店名「小鹏汽车武汉经开永旺销售中心」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -11550,7 +11550,7 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉江夏永旺销售中心</t>
+          <t>小鹏汽车武汉江宸龙湖天街销售中心</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
@@ -11565,12 +11565,12 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>湖北省武汉市江夏区文化大道199号永旺梦乐城1F-1062-2</t>
+          <t>湖北省武汉市江汉区青年路518号江宸龙湖天街负一楼小鹏汽车体验中心</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>连续在档 5 期；本期存在高相似店名「小鹏汽车武汉经开永旺销售中心」（疑似改名/合并，非真实关店）</t>
+          <t>连续在档 5 期</t>
         </is>
       </c>
     </row>
@@ -12318,7 +12318,7 @@
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•贵阳通源云岩</t>
+          <t>AITO授权用户中心•贵阳观山湖通源汽车文化广场</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
@@ -12333,7 +12333,7 @@
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>贵州省贵阳市云岩区新添大道南段485号</t>
+          <t>贵州省贵阳市观山湖区林城西路通源汽车文化广场一号钻石厅1楼</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
@@ -12350,7 +12350,7 @@
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•贵阳观山湖通源汽车文化广场</t>
+          <t>AITO授权用户中心•贵阳通源云岩</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
@@ -12365,7 +12365,7 @@
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>贵州省贵阳市观山湖区林城西路通源汽车文化广场一号钻石厅1楼</t>
+          <t>贵州省贵阳市云岩区新添大道南段485号</t>
         </is>
       </c>
       <c r="F47" s="3" t="inlineStr">
@@ -12446,7 +12446,7 @@
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>华为智能生活馆•西宁王府井百货</t>
+          <t>华为智能生活馆•西宁城东吾悦</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
@@ -12461,7 +12461,7 @@
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>青海省西宁市城中区西大街王府井百货B馆</t>
+          <t>青海省西宁市城东区八一路与民和路交叉口东南西宁城东吾悦广场</t>
         </is>
       </c>
       <c r="F50" s="3" t="inlineStr">
@@ -12510,7 +12510,7 @@
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>华为智能生活馆•西宁城东吾悦</t>
+          <t>华为智能生活馆•西宁王府井百货</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
@@ -12525,7 +12525,7 @@
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>青海省西宁市城东区八一路与民和路交叉口东南西宁城东吾悦广场</t>
+          <t>青海省西宁市城中区西大街王府井百货B馆</t>
         </is>
       </c>
       <c r="F52" s="3" t="inlineStr">
@@ -12596,17 +12596,17 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊潍州路销售服务中心</t>
+          <t>小鹏汽车海口南海大道销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊潍州路销售服务中心</t>
+          <t>小鹏汽车海口南海大道销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12616,7 +12616,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>山东省潍坊市奎文区潍州路2800号 → 潍坊市奎文区金宝乐园南100米路西</t>
+          <t>海南省海口市龙华区南海大道115号福德汽车城小鹏汽车 → 海南省海口市龙华区南海大道115号</t>
         </is>
       </c>
     </row>
@@ -12628,17 +12628,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12648,7 +12648,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>繁华大道29华天大厦向东20米3号整栋标准厂房 → 安徽省合肥市包河经济开发区繁华大道29华天大厦向东20米3号整栋标准厂房</t>
+          <t>河北省张家口市经济技术开发区张宣公路西侧白云街1号 → 河北省张家口市经济技术开发区白云街1号万国汽配城后</t>
         </is>
       </c>
     </row>
@@ -12660,17 +12660,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州海盛汽车城交付中心</t>
+          <t>小鹏汽车文山国际汽车城销售中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州海盛汽车城交付中心</t>
+          <t>小鹏汽车文山国际汽车城销售中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12680,7 +12680,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>福州市闽侯县荆溪镇永丰村洪甘路189号海盛汽车城 → 荆溪镇永丰村杜坞42号海盛汽车城A区5栋1层小鹏福州海盛交付中心</t>
+          <t>云南省文山壮族苗族自治州文山市腾龙北路世纪名苑二期 → 云南省文山壮族苗族自治州文山市腾龙北路世纪名苑B期第28-31号商铺</t>
         </is>
       </c>
     </row>
@@ -12692,17 +12692,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京五方天雅销售服务中心</t>
+          <t>小鹏汽车重庆万象城销售中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京五方天雅销售服务中心</t>
+          <t>小鹏汽车重庆万象城销售中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12712,29 +12712,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>北京市朝阳区王四营乡五方天雅B区B1-03 → 北京市朝阳区五方桥西南侧五方天雅市场内B区B1-03号</t>
+          <t>重庆市九龙坡区万象城北区 → 重庆市九龙坡区万象城北区3号门NL132</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小米之家湖南省长沙市岳麓区长沙万象城汽车体验店</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小米之家湖南省长沙市岳麓区长沙万象城汽车体验店</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12744,7 +12744,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>桐兴巷与铜盆湖路交叉口西北160米 → 湖南省长沙市岳麓区桐兴巷与铜盆湖路交叉口西北160米</t>
+          <t>青岛市市北区四流南路22号-8幢展厅 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心</t>
         </is>
       </c>
     </row>
@@ -12756,17 +12756,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海口南海大道销售服务中心</t>
+          <t>小鹏汽车潍坊潍州路销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海口南海大道销售服务中心</t>
+          <t>小鹏汽车潍坊潍州路销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12776,29 +12776,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>海南省海口市龙华区南海大道115号福德汽车城小鹏汽车 → 海南省海口市龙华区南海大道115号</t>
+          <t>山东省潍坊市奎文区潍州路2800号 → 潍坊市奎文区金宝乐园南100米路西</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆万象城销售中心</t>
+          <t>小米之家湖南省长沙市岳麓区长沙万象城汽车体验店</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆万象城销售中心</t>
+          <t>小米之家湖南省长沙市岳麓区长沙万象城汽车体验店</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12808,29 +12808,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>重庆市九龙坡区万象城北区 → 重庆市九龙坡区万象城北区3号门NL132</t>
+          <t>桐兴巷与铜盆湖路交叉口西北160米 → 湖南省长沙市岳麓区桐兴巷与铜盆湖路交叉口西北160米</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>广州市锦龙汽车发展有限公司</t>
+          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>广州市锦龙汽车发展有限公司</t>
+          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12840,7 +12840,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>广东省广州市天河区广东省广州市天河区黄村街道奥体路55号(奥林匹克体育中心东门对面) → 广东省广州市天河区奥体南路5号</t>
+          <t>繁华大道29华天大厦向东20米3号整栋标准厂房 → 安徽省合肥市包河经济开发区繁华大道29华天大厦向东20米3号整栋标准厂房</t>
         </is>
       </c>
     </row>
@@ -12852,17 +12852,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车文山国际汽车城销售中心</t>
+          <t>小鹏汽车天津北辰双江道销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车文山国际汽车城销售中心</t>
+          <t>小鹏汽车天津北辰双江道销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12872,29 +12872,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>云南省文山壮族苗族自治州文山市腾龙北路世纪名苑二期 → 云南省文山壮族苗族自治州文山市腾龙北路世纪名苑B期第28-31号商铺</t>
+          <t>天津市北辰区双街镇庞大汽贸园原五菱宝骏店展厅 → 天津市北辰区双街镇庞大汽贸园原五菱骏宝店展厅</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>上海德辰汽车销售有限公司</t>
+          <t>华为授权体验店（东吴银泰）</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>上海德辰汽车销售有限公司</t>
+          <t>华为授权体验店（东吴银泰）</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12904,29 +12904,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>上海市闵行区颛兴东路1280弄3号(都会路口) → 上海市闵行区莲花南路2333号</t>
+          <t>浙江省湖州市吴兴区劳动路518号湖州东吴银泰城1F层【1001-A,1001-B,1002、1-39】号 → 湖州市吴兴区劳动路518号湖州东吴银泰城1F层C馆（1001-A,1001-B,1002-C) 华为授权体验店</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津北辰双江道销售服务中心</t>
+          <t>上海德辰汽车销售有限公司</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津北辰双江道销售服务中心</t>
+          <t>上海德辰汽车销售有限公司</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12936,7 +12936,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>天津市北辰区双街镇庞大汽贸园原五菱宝骏店展厅 → 天津市北辰区双街镇庞大汽贸园原五菱骏宝店展厅</t>
+          <t>上海市闵行区颛兴东路1280弄3号(都会路口) → 上海市闵行区莲花南路2333号</t>
         </is>
       </c>
     </row>
@@ -12948,17 +12948,17 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小鹏汽车深圳福保销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小鹏汽车深圳福保销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12968,7 +12968,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
+          <t>深圳市福田保税区蓝花道6号诚联物流大厦1层 → 广东省深圳市福田区蓝花道6号城联物流大厦一层</t>
         </is>
       </c>
     </row>
@@ -12980,17 +12980,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
+          <t>小鹏汽车汕头龙湖销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
+          <t>小鹏汽车汕头龙湖销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -13000,29 +13000,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>四川省遂宁市遂宁高新区物流港物流大道858-888号 → 四川省遂宁市遂宁高新区物流港主干道B南侧858-888号</t>
+          <t>广东省汕头市龙湖区汕汾路与淮河路交界处北侧 → 汕头市龙湖区汕汾路与淮河路交界处北侧之一（东侧）</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>广州市锦龙汽车发展有限公司</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>广州市锦龙汽车发展有限公司</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -13032,7 +13032,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>河北省张家口市经济技术开发区张宣公路西侧白云街1号 → 河北省张家口市经济技术开发区白云街1号万国汽配城后</t>
+          <t>广东省广州市天河区广东省广州市天河区黄村街道奥体路55号(奥林匹克体育中心东门对面) → 广东省广州市天河区奥体南路5号</t>
         </is>
       </c>
     </row>
@@ -13044,17 +13044,17 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车乐山天牛汽车城销售服务中心</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车乐山天牛汽车城销售服务中心</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -13064,7 +13064,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>四川省乐山市市中区龙游路北段518号 → 四川省乐山市市中区龙游路北段518号1幢</t>
+          <t>新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅 → 新疆伊宁市巴彦岱城投汽车产业园</t>
         </is>
       </c>
     </row>
@@ -13081,12 +13081,12 @@
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳福保销售服务中心</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳福保销售服务中心</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13096,29 +13096,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>深圳市福田保税区蓝花道6号诚联物流大厦1层 → 广东省深圳市福田区蓝花道6号城联物流大厦一层</t>
+          <t>佛山市禅城区南庄镇醒群社村工业区5号 → 广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>昆明经开特斯拉中心</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>昆明经开特斯拉中心</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13128,7 +13128,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>云南省昆明市自由贸易试验区昆明片区经开区出口加工区A6-1-2号（宝泽路41号）2栋 → 云南省昆明市经济开发区宝泽路41号2栋</t>
+          <t>龙跃街9号院 顺义区马坡聚源工业园 101317 → 新东路幸福二村40号楼 朝阳区 100027</t>
         </is>
       </c>
     </row>
@@ -13140,17 +13140,17 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>小鹏汽车北京五方天雅销售服务中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>小鹏汽车北京五方天雅销售服务中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13160,7 +13160,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>佛山市禅城区南庄镇醒群社村工业区5号 → 广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号</t>
+          <t>北京市朝阳区王四营乡五方天雅B区B1-03 → 北京市朝阳区五方桥西南侧五方天雅市场内B区B1-03号</t>
         </is>
       </c>
     </row>
@@ -13172,17 +13172,17 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕头龙湖销售服务中心</t>
+          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕头龙湖销售服务中心</t>
+          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13192,29 +13192,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>广东省汕头市龙湖区汕汾路与淮河路交界处北侧 → 汕头市龙湖区汕汾路与淮河路交界处北侧之一（东侧）</t>
+          <t>四川省遂宁市遂宁高新区物流港物流大道858-888号 → 四川省遂宁市遂宁高新区物流港主干道B南侧858-888号</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13224,7 +13224,7 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>龙跃街9号院 顺义区马坡聚源工业园 101317 → 新东路幸福二村40号楼 朝阳区 100027</t>
+          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
         </is>
       </c>
     </row>
@@ -13268,17 +13268,17 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>小鹏汽车福州海盛汽车城交付中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>小鹏汽车福州海盛汽车城交付中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13288,29 +13288,29 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅 → 新疆伊宁市巴彦岱城投汽车产业园</t>
+          <t>福州市闽侯县荆溪镇永丰村洪甘路189号海盛汽车城 → 荆溪镇永丰村杜坞42号海盛汽车城A区5栋1层小鹏福州海盛交付中心</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（东吴银泰）</t>
+          <t>小鹏汽车乐山天牛汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（东吴银泰）</t>
+          <t>小鹏汽车乐山天牛汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13320,29 +13320,29 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>浙江省湖州市吴兴区劳动路518号湖州东吴银泰城1F层【1001-A,1001-B,1002、1-39】号 → 湖州市吴兴区劳动路518号湖州东吴银泰城1F层C馆（1001-A,1001-B,1002-C) 华为授权体验店</t>
+          <t>四川省乐山市市中区龙游路北段518号 → 四川省乐山市市中区龙游路北段518号1幢</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>昆明经开特斯拉中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>昆明经开特斯拉中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13352,7 +13352,7 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区四流南路22号-8幢展厅 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心</t>
+          <t>云南省昆明市自由贸易试验区昆明片区经开区出口加工区A6-1-2号（宝泽路41号）2栋 → 云南省昆明市经济开发区宝泽路41号2栋</t>
         </is>
       </c>
     </row>
@@ -13423,7 +13423,7 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
@@ -13433,12 +13433,12 @@
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>深圳光明蓝鲸世界体验店L1-07/08</t>
+          <t>华为智能生活馆•佛山岭南新天地</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>深圳光明蓝鲸世界体验店</t>
+          <t>华为智能生活馆•佛山岭南天地</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -13460,17 +13460,17 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>上海松江万达</t>
+          <t>深圳光明蓝鲸世界体验店L1-07/08</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>上海松江万达广场</t>
+          <t>深圳光明蓝鲸世界体验店</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -13487,22 +13487,22 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•佛山岭南新天地</t>
+          <t>宾利北京亦庄</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•佛山岭南天地</t>
+          <t>宾利北京五棵松（新）</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -13524,7 +13524,7 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
@@ -13583,22 +13583,22 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>宾利北京亦庄</t>
+          <t>上海松江万达</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>宾利北京五棵松（新）</t>
+          <t>上海松江万达广场</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260601_vs_20260608.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260601_vs_20260608.xlsx
@@ -11518,7 +11518,7 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉江夏永旺销售中心</t>
+          <t>小鹏汽车武汉江宸龙湖天街销售中心</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
@@ -11533,12 +11533,12 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>湖北省武汉市江夏区文化大道199号永旺梦乐城1F-1062-2</t>
+          <t>湖北省武汉市江汉区青年路518号江宸龙湖天街负一楼小鹏汽车体验中心</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>连续在档 5 期；本期存在高相似店名「小鹏汽车武汉经开永旺销售中心」（疑似改名/合并，非真实关店）</t>
+          <t>连续在档 5 期</t>
         </is>
       </c>
     </row>
@@ -11550,7 +11550,7 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉江宸龙湖天街销售中心</t>
+          <t>小鹏汽车武汉江夏永旺销售中心</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
@@ -11565,12 +11565,12 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>湖北省武汉市江汉区青年路518号江宸龙湖天街负一楼小鹏汽车体验中心</t>
+          <t>湖北省武汉市江夏区文化大道199号永旺梦乐城1F-1062-2</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>连续在档 5 期</t>
+          <t>连续在档 5 期；本期存在高相似店名「小鹏汽车武汉经开永旺销售中心」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -12318,7 +12318,7 @@
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•贵阳观山湖通源汽车文化广场</t>
+          <t>AITO授权用户中心•贵阳通源云岩</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
@@ -12333,7 +12333,7 @@
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>贵州省贵阳市观山湖区林城西路通源汽车文化广场一号钻石厅1楼</t>
+          <t>贵州省贵阳市云岩区新添大道南段485号</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
@@ -12350,7 +12350,7 @@
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•贵阳通源云岩</t>
+          <t>AITO授权用户中心•贵阳观山湖通源汽车文化广场</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
@@ -12365,7 +12365,7 @@
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>贵州省贵阳市云岩区新添大道南段485号</t>
+          <t>贵州省贵阳市观山湖区林城西路通源汽车文化广场一号钻石厅1楼</t>
         </is>
       </c>
       <c r="F47" s="3" t="inlineStr">
@@ -12446,7 +12446,7 @@
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>华为智能生活馆•西宁城东吾悦</t>
+          <t>华为智能生活馆•西宁王府井百货</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
@@ -12461,7 +12461,7 @@
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>青海省西宁市城东区八一路与民和路交叉口东南西宁城东吾悦广场</t>
+          <t>青海省西宁市城中区西大街王府井百货B馆</t>
         </is>
       </c>
       <c r="F50" s="3" t="inlineStr">
@@ -12510,7 +12510,7 @@
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>华为智能生活馆•西宁王府井百货</t>
+          <t>华为智能生活馆•西宁城东吾悦</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
@@ -12525,7 +12525,7 @@
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>青海省西宁市城中区西大街王府井百货B馆</t>
+          <t>青海省西宁市城东区八一路与民和路交叉口东南西宁城东吾悦广场</t>
         </is>
       </c>
       <c r="F52" s="3" t="inlineStr">
@@ -12591,22 +12591,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海口南海大道销售服务中心</t>
+          <t>上海德辰汽车销售有限公司</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海口南海大道销售服务中心</t>
+          <t>上海德辰汽车销售有限公司</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12616,7 +12616,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>海南省海口市龙华区南海大道115号福德汽车城小鹏汽车 → 海南省海口市龙华区南海大道115号</t>
+          <t>上海市闵行区颛兴东路1280弄3号(都会路口) → 上海市闵行区莲花南路2333号</t>
         </is>
       </c>
     </row>
@@ -12628,17 +12628,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>小鹏汽车汕头龙湖销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>小鹏汽车汕头龙湖销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12648,7 +12648,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>河北省张家口市经济技术开发区张宣公路西侧白云街1号 → 河北省张家口市经济技术开发区白云街1号万国汽配城后</t>
+          <t>广东省汕头市龙湖区汕汾路与淮河路交界处北侧 → 汕头市龙湖区汕汾路与淮河路交界处北侧之一（东侧）</t>
         </is>
       </c>
     </row>
@@ -12660,17 +12660,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车文山国际汽车城销售中心</t>
+          <t>小鹏汽车北京五方天雅销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车文山国际汽车城销售中心</t>
+          <t>小鹏汽车北京五方天雅销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12680,7 +12680,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>云南省文山壮族苗族自治州文山市腾龙北路世纪名苑二期 → 云南省文山壮族苗族自治州文山市腾龙北路世纪名苑B期第28-31号商铺</t>
+          <t>北京市朝阳区王四营乡五方天雅B区B1-03 → 北京市朝阳区五方桥西南侧五方天雅市场内B区B1-03号</t>
         </is>
       </c>
     </row>
@@ -12692,17 +12692,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆万象城销售中心</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆万象城销售中心</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12712,7 +12712,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>重庆市九龙坡区万象城北区 → 重庆市九龙坡区万象城北区3号门NL132</t>
+          <t>新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅 → 新疆伊宁市巴彦岱城投汽车产业园</t>
         </is>
       </c>
     </row>
@@ -12724,17 +12724,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车深圳福保销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车深圳福保销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12744,7 +12744,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区四流南路22号-8幢展厅 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心</t>
+          <t>深圳市福田保税区蓝花道6号诚联物流大厦1层 → 广东省深圳市福田区蓝花道6号城联物流大厦一层</t>
         </is>
       </c>
     </row>
@@ -12756,17 +12756,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊潍州路销售服务中心</t>
+          <t>小鹏汽车天津北辰双江道销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊潍州路销售服务中心</t>
+          <t>小鹏汽车天津北辰双江道销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12776,29 +12776,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>山东省潍坊市奎文区潍州路2800号 → 潍坊市奎文区金宝乐园南100米路西</t>
+          <t>天津市北辰区双街镇庞大汽贸园原五菱宝骏店展厅 → 天津市北辰区双街镇庞大汽贸园原五菱骏宝店展厅</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小米之家湖南省长沙市岳麓区长沙万象城汽车体验店</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小米之家湖南省长沙市岳麓区长沙万象城汽车体验店</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12808,7 +12808,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>桐兴巷与铜盆湖路交叉口西北160米 → 湖南省长沙市岳麓区桐兴巷与铜盆湖路交叉口西北160米</t>
+          <t>龙跃街9号院 顺义区马坡聚源工业园 101317 → 新东路幸福二村40号楼 朝阳区 100027</t>
         </is>
       </c>
     </row>
@@ -12820,17 +12820,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
+          <t>小鹏汽车广州龙溪大道销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
+          <t>小鹏汽车广州龙溪大道销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12840,29 +12840,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>繁华大道29华天大厦向东20米3号整栋标准厂房 → 安徽省合肥市包河经济开发区繁华大道29华天大厦向东20米3号整栋标准厂房</t>
+          <t>广东省广州市荔湾区龙溪大道488号场内自编号为86号 → 广东省广州市荔湾区龙溪大道488号金马汽车交易城小鹏汽车</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津北辰双江道销售服务中心</t>
+          <t>华为授权体验店（东吴银泰）</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津北辰双江道销售服务中心</t>
+          <t>华为授权体验店（东吴银泰）</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12872,29 +12872,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>天津市北辰区双街镇庞大汽贸园原五菱宝骏店展厅 → 天津市北辰区双街镇庞大汽贸园原五菱骏宝店展厅</t>
+          <t>浙江省湖州市吴兴区劳动路518号湖州东吴银泰城1F层【1001-A,1001-B,1002、1-39】号 → 湖州市吴兴区劳动路518号湖州东吴银泰城1F层C馆（1001-A,1001-B,1002-C) 华为授权体验店</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（东吴银泰）</t>
+          <t>小鹏汽车重庆万象城销售中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（东吴银泰）</t>
+          <t>小鹏汽车重庆万象城销售中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12904,29 +12904,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>浙江省湖州市吴兴区劳动路518号湖州东吴银泰城1F层【1001-A,1001-B,1002、1-39】号 → 湖州市吴兴区劳动路518号湖州东吴银泰城1F层C馆（1001-A,1001-B,1002-C) 华为授权体验店</t>
+          <t>重庆市九龙坡区万象城北区 → 重庆市九龙坡区万象城北区3号门NL132</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>上海德辰汽车销售有限公司</t>
+          <t>小鹏汽车乐山天牛汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>上海德辰汽车销售有限公司</t>
+          <t>小鹏汽车乐山天牛汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12936,7 +12936,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>上海市闵行区颛兴东路1280弄3号(都会路口) → 上海市闵行区莲花南路2333号</t>
+          <t>四川省乐山市市中区龙游路北段518号 → 四川省乐山市市中区龙游路北段518号1幢</t>
         </is>
       </c>
     </row>
@@ -12948,17 +12948,17 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳福保销售服务中心</t>
+          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳福保销售服务中心</t>
+          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12968,29 +12968,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>深圳市福田保税区蓝花道6号诚联物流大厦1层 → 广东省深圳市福田区蓝花道6号城联物流大厦一层</t>
+          <t>繁华大道29华天大厦向东20米3号整栋标准厂房 → 安徽省合肥市包河经济开发区繁华大道29华天大厦向东20米3号整栋标准厂房</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕头龙湖销售服务中心</t>
+          <t>小米之家湖南省长沙市岳麓区长沙万象城汽车体验店</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕头龙湖销售服务中心</t>
+          <t>小米之家湖南省长沙市岳麓区长沙万象城汽车体验店</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -13000,29 +13000,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>广东省汕头市龙湖区汕汾路与淮河路交界处北侧 → 汕头市龙湖区汕汾路与淮河路交界处北侧之一（东侧）</t>
+          <t>桐兴巷与铜盆湖路交叉口西北160米 → 湖南省长沙市岳麓区桐兴巷与铜盆湖路交叉口西北160米</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>广州市锦龙汽车发展有限公司</t>
+          <t>小鹏汽车潍坊潍州路销售服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>广州市锦龙汽车发展有限公司</t>
+          <t>小鹏汽车潍坊潍州路销售服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -13032,7 +13032,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>广东省广州市天河区广东省广州市天河区黄村街道奥体路55号(奥林匹克体育中心东门对面) → 广东省广州市天河区奥体南路5号</t>
+          <t>山东省潍坊市奎文区潍州路2800号 → 潍坊市奎文区金宝乐园南100米路西</t>
         </is>
       </c>
     </row>
@@ -13044,17 +13044,17 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>小鹏汽车海口南海大道销售服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>小鹏汽车海口南海大道销售服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -13064,7 +13064,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅 → 新疆伊宁市巴彦岱城投汽车产业园</t>
+          <t>海南省海口市龙华区南海大道115号福德汽车城小鹏汽车 → 海南省海口市龙华区南海大道115号</t>
         </is>
       </c>
     </row>
@@ -13076,17 +13076,17 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13096,29 +13096,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>佛山市禅城区南庄镇醒群社村工业区5号 → 广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号</t>
+          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>广州市锦龙汽车发展有限公司</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>广州市锦龙汽车发展有限公司</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13128,7 +13128,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>龙跃街9号院 顺义区马坡聚源工业园 101317 → 新东路幸福二村40号楼 朝阳区 100027</t>
+          <t>广东省广州市天河区广东省广州市天河区黄村街道奥体路55号(奥林匹克体育中心东门对面) → 广东省广州市天河区奥体南路5号</t>
         </is>
       </c>
     </row>
@@ -13140,17 +13140,17 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京五方天雅销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京五方天雅销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13160,7 +13160,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>北京市朝阳区王四营乡五方天雅B区B1-03 → 北京市朝阳区五方桥西南侧五方天雅市场内B区B1-03号</t>
+          <t>青岛市市北区四流南路22号-8幢展厅 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心</t>
         </is>
       </c>
     </row>
@@ -13172,17 +13172,17 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13192,7 +13192,7 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>四川省遂宁市遂宁高新区物流港物流大道858-888号 → 四川省遂宁市遂宁高新区物流港主干道B南侧858-888号</t>
+          <t>佛山市禅城区南庄镇醒群社村工业区5号 → 广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号</t>
         </is>
       </c>
     </row>
@@ -13204,17 +13204,17 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小鹏汽车文山国际汽车城销售中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小鹏汽车文山国际汽车城销售中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13224,7 +13224,7 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
+          <t>云南省文山壮族苗族自治州文山市腾龙北路世纪名苑二期 → 云南省文山壮族苗族自治州文山市腾龙北路世纪名苑B期第28-31号商铺</t>
         </is>
       </c>
     </row>
@@ -13236,17 +13236,17 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州龙溪大道销售服务中心</t>
+          <t>小鹏汽车福州海盛汽车城交付中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州龙溪大道销售服务中心</t>
+          <t>小鹏汽车福州海盛汽车城交付中心</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13256,29 +13256,29 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>广东省广州市荔湾区龙溪大道488号场内自编号为86号 → 广东省广州市荔湾区龙溪大道488号金马汽车交易城小鹏汽车</t>
+          <t>福州市闽侯县荆溪镇永丰村洪甘路189号海盛汽车城 → 荆溪镇永丰村杜坞42号海盛汽车城A区5栋1层小鹏福州海盛交付中心</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州海盛汽车城交付中心</t>
+          <t>昆明经开特斯拉中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州海盛汽车城交付中心</t>
+          <t>昆明经开特斯拉中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13288,7 +13288,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>福州市闽侯县荆溪镇永丰村洪甘路189号海盛汽车城 → 荆溪镇永丰村杜坞42号海盛汽车城A区5栋1层小鹏福州海盛交付中心</t>
+          <t>云南省昆明市自由贸易试验区昆明片区经开区出口加工区A6-1-2号（宝泽路41号）2栋 → 云南省昆明市经济开发区宝泽路41号2栋</t>
         </is>
       </c>
     </row>
@@ -13300,17 +13300,17 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车乐山天牛汽车城销售服务中心</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车乐山天牛汽车城销售服务中心</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13320,29 +13320,29 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>四川省乐山市市中区龙游路北段518号 → 四川省乐山市市中区龙游路北段518号1幢</t>
+          <t>河北省张家口市经济技术开发区张宣公路西侧白云街1号 → 河北省张家口市经济技术开发区白云街1号万国汽配城后</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>昆明经开特斯拉中心</t>
+          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>昆明经开特斯拉中心</t>
+          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13352,7 +13352,7 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>云南省昆明市自由贸易试验区昆明片区经开区出口加工区A6-1-2号（宝泽路41号）2栋 → 云南省昆明市经济开发区宝泽路41号2栋</t>
+          <t>四川省遂宁市遂宁高新区物流港物流大道858-888号 → 四川省遂宁市遂宁高新区物流港主干道B南侧858-888号</t>
         </is>
       </c>
     </row>
@@ -13423,22 +13423,22 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•佛山岭南新天地</t>
+          <t>上海松江万达</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•佛山岭南天地</t>
+          <t>上海松江万达广场</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -13551,22 +13551,22 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海临港万达广场销售中心</t>
+          <t>华为智能生活馆•佛山岭南新天地</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海临港万达销售展厅</t>
+          <t>华为智能生活馆•佛山岭南天地</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -13583,7 +13583,7 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
@@ -13593,12 +13593,12 @@
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>上海松江万达</t>
+          <t>小鹏汽车上海临港万达广场销售中心</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>上海松江万达广场</t>
+          <t>小鹏汽车上海临港万达销售展厅</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -13652,17 +13652,17 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（相城龙湖）</t>
+          <t>华为智能生活馆•蚌埠银泰</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（永旺梦乐城）</t>
+          <t>华为智能生活馆•蚌埠银泰城</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -13672,7 +13672,7 @@
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 100%</t>
+          <t>店名相似度 96%</t>
         </is>
       </c>
     </row>
@@ -13684,17 +13684,17 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•蚌埠银泰</t>
+          <t>华为授权体验店（相城龙湖）</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•蚌埠银泰城</t>
+          <t>华为授权体验店（永旺梦乐城）</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -13704,7 +13704,7 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 96%</t>
+          <t>店名相似度 100%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260601_vs_20260608.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260601_vs_20260608.xlsx
@@ -11518,7 +11518,7 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉江宸龙湖天街销售中心</t>
+          <t>小鹏汽车武汉江夏永旺销售中心</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
@@ -11533,12 +11533,12 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>湖北省武汉市江汉区青年路518号江宸龙湖天街负一楼小鹏汽车体验中心</t>
+          <t>湖北省武汉市江夏区文化大道199号永旺梦乐城1F-1062-2</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>连续在档 5 期</t>
+          <t>连续在档 5 期；本期存在高相似店名「小鹏汽车武汉经开永旺销售中心」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -11550,7 +11550,7 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉江夏永旺销售中心</t>
+          <t>小鹏汽车武汉江宸龙湖天街销售中心</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
@@ -11565,12 +11565,12 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>湖北省武汉市江夏区文化大道199号永旺梦乐城1F-1062-2</t>
+          <t>湖北省武汉市江汉区青年路518号江宸龙湖天街负一楼小鹏汽车体验中心</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>连续在档 5 期；本期存在高相似店名「小鹏汽车武汉经开永旺销售中心」（疑似改名/合并，非真实关店）</t>
+          <t>连续在档 5 期</t>
         </is>
       </c>
     </row>
@@ -11582,7 +11582,7 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>小鹏汽车西安王府井销售中心</t>
+          <t>小鹏汽车西安芙蓉新天地销售中心</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
@@ -11597,7 +11597,7 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>陕西省西安市未央区未央路170号熙地港负一层王府井新能源展厅</t>
+          <t>西安市曲江新区芙蓉南路芙蓉新天地购物中心1F-F1005</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
@@ -11614,7 +11614,7 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>小鹏汽车西安芙蓉新天地销售中心</t>
+          <t>小鹏汽车西安王府井销售中心</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -11629,7 +11629,7 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>西安市曲江新区芙蓉南路芙蓉新天地购物中心1F-F1005</t>
+          <t>陕西省西安市未央区未央路170号熙地港负一层王府井新能源展厅</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
@@ -12094,7 +12094,7 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>华为授权体验店（融创广场）</t>
+          <t>华为授权体验店（相城龙湖）</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
@@ -12104,12 +12104,12 @@
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>淮安市</t>
+          <t>苏州市</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 江苏省淮安市清江浦区天津路融创广场一楼华为</t>
+          <t>江苏省苏州市相城区相城大道1399号龙湖天街一层A1F-25、26号</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
@@ -12446,7 +12446,7 @@
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>华为智能生活馆•西宁王府井百货</t>
+          <t>华为智能生活馆•西宁城东吾悦</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
@@ -12461,7 +12461,7 @@
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>青海省西宁市城中区西大街王府井百货B馆</t>
+          <t>青海省西宁市城东区八一路与民和路交叉口东南西宁城东吾悦广场</t>
         </is>
       </c>
       <c r="F50" s="3" t="inlineStr">
@@ -12510,7 +12510,7 @@
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>华为智能生活馆•西宁城东吾悦</t>
+          <t>华为智能生活馆•西宁王府井百货</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
@@ -12525,7 +12525,7 @@
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>青海省西宁市城东区八一路与民和路交叉口东南西宁城东吾悦广场</t>
+          <t>青海省西宁市城中区西大街王府井百货B馆</t>
         </is>
       </c>
       <c r="F52" s="3" t="inlineStr">
@@ -12591,22 +12591,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>上海德辰汽车销售有限公司</t>
+          <t>小鹏汽车海口南海大道销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>上海德辰汽车销售有限公司</t>
+          <t>小鹏汽车海口南海大道销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12616,7 +12616,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>上海市闵行区颛兴东路1280弄3号(都会路口) → 上海市闵行区莲花南路2333号</t>
+          <t>海南省海口市龙华区南海大道115号福德汽车城小鹏汽车 → 海南省海口市龙华区南海大道115号</t>
         </is>
       </c>
     </row>
@@ -12628,17 +12628,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕头龙湖销售服务中心</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕头龙湖销售服务中心</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12648,7 +12648,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>广东省汕头市龙湖区汕汾路与淮河路交界处北侧 → 汕头市龙湖区汕汾路与淮河路交界处北侧之一（东侧）</t>
+          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
         </is>
       </c>
     </row>
@@ -12660,17 +12660,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京五方天雅销售服务中心</t>
+          <t>小鹏汽车汕头龙湖销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京五方天雅销售服务中心</t>
+          <t>小鹏汽车汕头龙湖销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12680,7 +12680,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>北京市朝阳区王四营乡五方天雅B区B1-03 → 北京市朝阳区五方桥西南侧五方天雅市场内B区B1-03号</t>
+          <t>广东省汕头市龙湖区汕汾路与淮河路交界处北侧 → 汕头市龙湖区汕汾路与淮河路交界处北侧之一（东侧）</t>
         </is>
       </c>
     </row>
@@ -12692,17 +12692,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>小鹏汽车北京五方天雅销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>小鹏汽车北京五方天雅销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12712,7 +12712,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅 → 新疆伊宁市巴彦岱城投汽车产业园</t>
+          <t>北京市朝阳区王四营乡五方天雅B区B1-03 → 北京市朝阳区五方桥西南侧五方天雅市场内B区B1-03号</t>
         </is>
       </c>
     </row>
@@ -12724,17 +12724,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳福保销售服务中心</t>
+          <t>小鹏汽车重庆万象城销售中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳福保销售服务中心</t>
+          <t>小鹏汽车重庆万象城销售中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12744,7 +12744,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>深圳市福田保税区蓝花道6号诚联物流大厦1层 → 广东省深圳市福田区蓝花道6号城联物流大厦一层</t>
+          <t>重庆市九龙坡区万象城北区 → 重庆市九龙坡区万象城北区3号门NL132</t>
         </is>
       </c>
     </row>
@@ -12756,17 +12756,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津北辰双江道销售服务中心</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津北辰双江道销售服务中心</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12776,29 +12776,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>天津市北辰区双街镇庞大汽贸园原五菱宝骏店展厅 → 天津市北辰区双街镇庞大汽贸园原五菱骏宝店展厅</t>
+          <t>新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅 → 新疆伊宁市巴彦岱城投汽车产业园</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>小鹏汽车广州龙溪大道销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>小鹏汽车广州龙溪大道销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12808,29 +12808,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>龙跃街9号院 顺义区马坡聚源工业园 101317 → 新东路幸福二村40号楼 朝阳区 100027</t>
+          <t>广东省广州市荔湾区龙溪大道488号场内自编号为86号 → 广东省广州市荔湾区龙溪大道488号金马汽车交易城小鹏汽车</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州龙溪大道销售服务中心</t>
+          <t>昆明经开特斯拉中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州龙溪大道销售服务中心</t>
+          <t>昆明经开特斯拉中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12840,7 +12840,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>广东省广州市荔湾区龙溪大道488号场内自编号为86号 → 广东省广州市荔湾区龙溪大道488号金马汽车交易城小鹏汽车</t>
+          <t>云南省昆明市自由贸易试验区昆明片区经开区出口加工区A6-1-2号（宝泽路41号）2栋 → 云南省昆明市经济开发区宝泽路41号2栋</t>
         </is>
       </c>
     </row>
@@ -12879,22 +12879,22 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆万象城销售中心</t>
+          <t>上海德辰汽车销售有限公司</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆万象城销售中心</t>
+          <t>上海德辰汽车销售有限公司</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12904,29 +12904,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>重庆市九龙坡区万象城北区 → 重庆市九龙坡区万象城北区3号门NL132</t>
+          <t>上海市闵行区颛兴东路1280弄3号(都会路口) → 上海市闵行区莲花南路2333号</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车乐山天牛汽车城销售服务中心</t>
+          <t>广州市锦龙汽车发展有限公司</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车乐山天牛汽车城销售服务中心</t>
+          <t>广州市锦龙汽车发展有限公司</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12936,7 +12936,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>四川省乐山市市中区龙游路北段518号 → 四川省乐山市市中区龙游路北段518号1幢</t>
+          <t>广东省广州市天河区广东省广州市天河区黄村街道奥体路55号(奥林匹克体育中心东门对面) → 广东省广州市天河区奥体南路5号</t>
         </is>
       </c>
     </row>
@@ -12948,17 +12948,17 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12968,29 +12968,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>繁华大道29华天大厦向东20米3号整栋标准厂房 → 安徽省合肥市包河经济开发区繁华大道29华天大厦向东20米3号整栋标准厂房</t>
+          <t>佛山市禅城区南庄镇醒群社村工业区5号 → 广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小米之家湖南省长沙市岳麓区长沙万象城汽车体验店</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小米之家湖南省长沙市岳麓区长沙万象城汽车体验店</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -13000,7 +13000,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>桐兴巷与铜盆湖路交叉口西北160米 → 湖南省长沙市岳麓区桐兴巷与铜盆湖路交叉口西北160米</t>
+          <t>河北省张家口市经济技术开发区张宣公路西侧白云街1号 → 河北省张家口市经济技术开发区白云街1号万国汽配城后</t>
         </is>
       </c>
     </row>
@@ -13012,17 +13012,17 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊潍州路销售服务中心</t>
+          <t>小鹏汽车深圳福保销售服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊潍州路销售服务中心</t>
+          <t>小鹏汽车深圳福保销售服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -13032,7 +13032,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>山东省潍坊市奎文区潍州路2800号 → 潍坊市奎文区金宝乐园南100米路西</t>
+          <t>深圳市福田保税区蓝花道6号诚联物流大厦1层 → 广东省深圳市福田区蓝花道6号城联物流大厦一层</t>
         </is>
       </c>
     </row>
@@ -13044,17 +13044,17 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海口南海大道销售服务中心</t>
+          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海口南海大道销售服务中心</t>
+          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -13064,7 +13064,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>海南省海口市龙华区南海大道115号福德汽车城小鹏汽车 → 海南省海口市龙华区南海大道115号</t>
+          <t>四川省遂宁市遂宁高新区物流港物流大道858-888号 → 四川省遂宁市遂宁高新区物流港主干道B南侧858-888号</t>
         </is>
       </c>
     </row>
@@ -13076,17 +13076,17 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小鹏汽车潍坊潍州路销售服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小鹏汽车潍坊潍州路销售服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13096,29 +13096,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
+          <t>山东省潍坊市奎文区潍州路2800号 → 潍坊市奎文区金宝乐园南100米路西</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>广州市锦龙汽车发展有限公司</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>广州市锦龙汽车发展有限公司</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13128,7 +13128,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>广东省广州市天河区广东省广州市天河区黄村街道奥体路55号(奥林匹克体育中心东门对面) → 广东省广州市天河区奥体南路5号</t>
+          <t>龙跃街9号院 顺义区马坡聚源工业园 101317 → 新东路幸福二村40号楼 朝阳区 100027</t>
         </is>
       </c>
     </row>
@@ -13140,17 +13140,17 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车文山国际汽车城销售中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车文山国际汽车城销售中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13160,29 +13160,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区四流南路22号-8幢展厅 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心</t>
+          <t>云南省文山壮族苗族自治州文山市腾龙北路世纪名苑二期 → 云南省文山壮族苗族自治州文山市腾龙北路世纪名苑B期第28-31号商铺</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>小米之家湖南省长沙市岳麓区长沙万象城汽车体验店</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>小米之家湖南省长沙市岳麓区长沙万象城汽车体验店</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13192,7 +13192,7 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>佛山市禅城区南庄镇醒群社村工业区5号 → 广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号</t>
+          <t>桐兴巷与铜盆湖路交叉口西北160米 → 湖南省长沙市岳麓区桐兴巷与铜盆湖路交叉口西北160米</t>
         </is>
       </c>
     </row>
@@ -13204,17 +13204,17 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车文山国际汽车城销售中心</t>
+          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车文山国际汽车城销售中心</t>
+          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13224,7 +13224,7 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>云南省文山壮族苗族自治州文山市腾龙北路世纪名苑二期 → 云南省文山壮族苗族自治州文山市腾龙北路世纪名苑B期第28-31号商铺</t>
+          <t>繁华大道29华天大厦向东20米3号整栋标准厂房 → 安徽省合肥市包河经济开发区繁华大道29华天大厦向东20米3号整栋标准厂房</t>
         </is>
       </c>
     </row>
@@ -13236,17 +13236,17 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州海盛汽车城交付中心</t>
+          <t>小鹏汽车乐山天牛汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州海盛汽车城交付中心</t>
+          <t>小鹏汽车乐山天牛汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13256,29 +13256,29 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>福州市闽侯县荆溪镇永丰村洪甘路189号海盛汽车城 → 荆溪镇永丰村杜坞42号海盛汽车城A区5栋1层小鹏福州海盛交付中心</t>
+          <t>四川省乐山市市中区龙游路北段518号 → 四川省乐山市市中区龙游路北段518号1幢</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>昆明经开特斯拉中心</t>
+          <t>小鹏汽车福州海盛汽车城交付中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>昆明经开特斯拉中心</t>
+          <t>小鹏汽车福州海盛汽车城交付中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13288,7 +13288,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>云南省昆明市自由贸易试验区昆明片区经开区出口加工区A6-1-2号（宝泽路41号）2栋 → 云南省昆明市经济开发区宝泽路41号2栋</t>
+          <t>福州市闽侯县荆溪镇永丰村洪甘路189号海盛汽车城 → 荆溪镇永丰村杜坞42号海盛汽车城A区5栋1层小鹏福州海盛交付中心</t>
         </is>
       </c>
     </row>
@@ -13300,17 +13300,17 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>小鹏汽车天津北辰双江道销售服务中心</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>小鹏汽车天津北辰双江道销售服务中心</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13320,7 +13320,7 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>河北省张家口市经济技术开发区张宣公路西侧白云街1号 → 河北省张家口市经济技术开发区白云街1号万国汽配城后</t>
+          <t>天津市北辰区双街镇庞大汽贸园原五菱宝骏店展厅 → 天津市北辰区双街镇庞大汽贸园原五菱骏宝店展厅</t>
         </is>
       </c>
     </row>
@@ -13332,17 +13332,17 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13352,7 +13352,7 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>四川省遂宁市遂宁高新区物流港物流大道858-888号 → 四川省遂宁市遂宁高新区物流港主干道B南侧858-888号</t>
+          <t>青岛市市北区四流南路22号-8幢展厅 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心</t>
         </is>
       </c>
     </row>
@@ -13423,22 +13423,22 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>上海松江万达</t>
+          <t>宾利北京亦庄</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>上海松江万达广场</t>
+          <t>宾利北京五棵松（新）</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -13455,22 +13455,22 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>深圳光明蓝鲸世界体验店L1-07/08</t>
+          <t>小鹏汽车上海临港万达广场销售中心</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>深圳光明蓝鲸世界体验店</t>
+          <t>小鹏汽车上海临港万达销售展厅</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -13487,22 +13487,22 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>宾利北京亦庄</t>
+          <t>深圳光明蓝鲸世界体验店L1-07/08</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>宾利北京五棵松（新）</t>
+          <t>深圳光明蓝鲸世界体验店</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -13519,22 +13519,22 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>宾利北京亦庄</t>
+          <t>上海松江万达</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>宾利北京五棵松（新）</t>
+          <t>上海松江万达广场</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -13551,22 +13551,22 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•佛山岭南新天地</t>
+          <t>宾利北京亦庄</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•佛山岭南天地</t>
+          <t>宾利北京五棵松（新）</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -13583,22 +13583,22 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海临港万达广场销售中心</t>
+          <t>华为智能生活馆•佛山岭南新天地</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海临港万达销售展厅</t>
+          <t>华为智能生活馆•佛山岭南天地</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -13689,7 +13689,7 @@
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（相城龙湖）</t>
+          <t>华为授权体验店（融创广场）</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260601_vs_20260608.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260601_vs_20260608.xlsx
@@ -12478,7 +12478,7 @@
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>华为智能生活馆•西宁海湖万达</t>
+          <t>华为智能生活馆•西宁王府井百货</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
@@ -12493,7 +12493,7 @@
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>青海省西宁市城西区海湖新区西关大街海湖万达广场2号门左侧</t>
+          <t>青海省西宁市城中区西大街王府井百货B馆</t>
         </is>
       </c>
       <c r="F51" s="3" t="inlineStr">
@@ -12510,7 +12510,7 @@
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>华为智能生活馆•西宁王府井百货</t>
+          <t>华为智能生活馆•西宁海湖万达</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
@@ -12525,7 +12525,7 @@
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>青海省西宁市城中区西大街王府井百货B馆</t>
+          <t>青海省西宁市城西区海湖新区西关大街海湖万达广场2号门左侧</t>
         </is>
       </c>
       <c r="F52" s="3" t="inlineStr">
@@ -12596,17 +12596,17 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海口南海大道销售服务中心</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海口南海大道销售服务中心</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12616,7 +12616,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>海南省海口市龙华区南海大道115号福德汽车城小鹏汽车 → 海南省海口市龙华区南海大道115号</t>
+          <t>新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅 → 新疆伊宁市巴彦岱城投汽车产业园</t>
         </is>
       </c>
     </row>
@@ -12628,17 +12628,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小鹏汽车天津北辰双江道销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小鹏汽车天津北辰双江道销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12648,7 +12648,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
+          <t>天津市北辰区双街镇庞大汽贸园原五菱宝骏店展厅 → 天津市北辰区双街镇庞大汽贸园原五菱骏宝店展厅</t>
         </is>
       </c>
     </row>
@@ -12660,17 +12660,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕头龙湖销售服务中心</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕头龙湖销售服务中心</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12680,29 +12680,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>广东省汕头市龙湖区汕汾路与淮河路交界处北侧 → 汕头市龙湖区汕汾路与淮河路交界处北侧之一（东侧）</t>
+          <t>河北省张家口市经济技术开发区张宣公路西侧白云街1号 → 河北省张家口市经济技术开发区白云街1号万国汽配城后</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京五方天雅销售服务中心</t>
+          <t>华为授权体验店（东吴银泰）</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京五方天雅销售服务中心</t>
+          <t>华为授权体验店（东吴银泰）</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12712,7 +12712,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>北京市朝阳区王四营乡五方天雅B区B1-03 → 北京市朝阳区五方桥西南侧五方天雅市场内B区B1-03号</t>
+          <t>浙江省湖州市吴兴区劳动路518号湖州东吴银泰城1F层【1001-A,1001-B,1002、1-39】号 → 湖州市吴兴区劳动路518号湖州东吴银泰城1F层C馆（1001-A,1001-B,1002-C) 华为授权体验店</t>
         </is>
       </c>
     </row>
@@ -12724,17 +12724,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆万象城销售中心</t>
+          <t>小鹏汽车汕头龙湖销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆万象城销售中心</t>
+          <t>小鹏汽车汕头龙湖销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12744,29 +12744,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>重庆市九龙坡区万象城北区 → 重庆市九龙坡区万象城北区3号门NL132</t>
+          <t>广东省汕头市龙湖区汕汾路与淮河路交界处北侧 → 汕头市龙湖区汕汾路与淮河路交界处北侧之一（东侧）</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>小米之家湖南省长沙市岳麓区长沙万象城汽车体验店</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>小米之家湖南省长沙市岳麓区长沙万象城汽车体验店</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12776,7 +12776,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅 → 新疆伊宁市巴彦岱城投汽车产业园</t>
+          <t>桐兴巷与铜盆湖路交叉口西北160米 → 湖南省长沙市岳麓区桐兴巷与铜盆湖路交叉口西北160米</t>
         </is>
       </c>
     </row>
@@ -12788,17 +12788,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州龙溪大道销售服务中心</t>
+          <t>小鹏汽车潍坊潍州路销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州龙溪大道销售服务中心</t>
+          <t>小鹏汽车潍坊潍州路销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12808,29 +12808,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>广东省广州市荔湾区龙溪大道488号场内自编号为86号 → 广东省广州市荔湾区龙溪大道488号金马汽车交易城小鹏汽车</t>
+          <t>山东省潍坊市奎文区潍州路2800号 → 潍坊市奎文区金宝乐园南100米路西</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>昆明经开特斯拉中心</t>
+          <t>广州市锦龙汽车发展有限公司</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>昆明经开特斯拉中心</t>
+          <t>广州市锦龙汽车发展有限公司</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12840,29 +12840,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>云南省昆明市自由贸易试验区昆明片区经开区出口加工区A6-1-2号（宝泽路41号）2栋 → 云南省昆明市经济开发区宝泽路41号2栋</t>
+          <t>广东省广州市天河区广东省广州市天河区黄村街道奥体路55号(奥林匹克体育中心东门对面) → 广东省广州市天河区奥体南路5号</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（东吴银泰）</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（东吴银泰）</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12872,29 +12872,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>浙江省湖州市吴兴区劳动路518号湖州东吴银泰城1F层【1001-A,1001-B,1002、1-39】号 → 湖州市吴兴区劳动路518号湖州东吴银泰城1F层C馆（1001-A,1001-B,1002-C) 华为授权体验店</t>
+          <t>龙跃街9号院 顺义区马坡聚源工业园 101317 → 新东路幸福二村40号楼 朝阳区 100027</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>上海德辰汽车销售有限公司</t>
+          <t>小鹏汽车海口南海大道销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>上海德辰汽车销售有限公司</t>
+          <t>小鹏汽车海口南海大道销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12904,14 +12904,14 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>上海市闵行区颛兴东路1280弄3号(都会路口) → 上海市闵行区莲花南路2333号</t>
+          <t>海南省海口市龙华区南海大道115号福德汽车城小鹏汽车 → 海南省海口市龙华区南海大道115号</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
@@ -12921,12 +12921,12 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>广州市锦龙汽车发展有限公司</t>
+          <t>小鹏汽车广州龙溪大道销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>广州市锦龙汽车发展有限公司</t>
+          <t>小鹏汽车广州龙溪大道销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12936,7 +12936,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>广东省广州市天河区广东省广州市天河区黄村街道奥体路55号(奥林匹克体育中心东门对面) → 广东省广州市天河区奥体南路5号</t>
+          <t>广东省广州市荔湾区龙溪大道488号场内自编号为86号 → 广东省广州市荔湾区龙溪大道488号金马汽车交易城小鹏汽车</t>
         </is>
       </c>
     </row>
@@ -12948,17 +12948,17 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>小鹏汽车重庆万象城销售中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>小鹏汽车重庆万象城销售中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12968,7 +12968,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>佛山市禅城区南庄镇醒群社村工业区5号 → 广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号</t>
+          <t>重庆市九龙坡区万象城北区 → 重庆市九龙坡区万象城北区3号门NL132</t>
         </is>
       </c>
     </row>
@@ -12980,17 +12980,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>小鹏汽车深圳福保销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>小鹏汽车深圳福保销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -13000,7 +13000,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>河北省张家口市经济技术开发区张宣公路西侧白云街1号 → 河北省张家口市经济技术开发区白云街1号万国汽配城后</t>
+          <t>深圳市福田保税区蓝花道6号诚联物流大厦1层 → 广东省深圳市福田区蓝花道6号城联物流大厦一层</t>
         </is>
       </c>
     </row>
@@ -13012,17 +13012,17 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳福保销售服务中心</t>
+          <t>小鹏汽车文山国际汽车城销售中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳福保销售服务中心</t>
+          <t>小鹏汽车文山国际汽车城销售中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -13032,7 +13032,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>深圳市福田保税区蓝花道6号诚联物流大厦1层 → 广东省深圳市福田区蓝花道6号城联物流大厦一层</t>
+          <t>云南省文山壮族苗族自治州文山市腾龙北路世纪名苑二期 → 云南省文山壮族苗族自治州文山市腾龙北路世纪名苑B期第28-31号商铺</t>
         </is>
       </c>
     </row>
@@ -13044,17 +13044,17 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -13064,29 +13064,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>四川省遂宁市遂宁高新区物流港物流大道858-888号 → 四川省遂宁市遂宁高新区物流港主干道B南侧858-888号</t>
+          <t>佛山市禅城区南庄镇醒群社村工业区5号 → 广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊潍州路销售服务中心</t>
+          <t>上海德辰汽车销售有限公司</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊潍州路销售服务中心</t>
+          <t>上海德辰汽车销售有限公司</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13096,29 +13096,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>山东省潍坊市奎文区潍州路2800号 → 潍坊市奎文区金宝乐园南100米路西</t>
+          <t>上海市闵行区颛兴东路1280弄3号(都会路口) → 上海市闵行区莲花南路2333号</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13128,7 +13128,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>龙跃街9号院 顺义区马坡聚源工业园 101317 → 新东路幸福二村40号楼 朝阳区 100027</t>
+          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
         </is>
       </c>
     </row>
@@ -13140,17 +13140,17 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车文山国际汽车城销售中心</t>
+          <t>小鹏汽车北京五方天雅销售服务中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车文山国际汽车城销售中心</t>
+          <t>小鹏汽车北京五方天雅销售服务中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13160,29 +13160,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>云南省文山壮族苗族自治州文山市腾龙北路世纪名苑二期 → 云南省文山壮族苗族自治州文山市腾龙北路世纪名苑B期第28-31号商铺</t>
+          <t>北京市朝阳区王四营乡五方天雅B区B1-03 → 北京市朝阳区五方桥西南侧五方天雅市场内B区B1-03号</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小米之家湖南省长沙市岳麓区长沙万象城汽车体验店</t>
+          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小米之家湖南省长沙市岳麓区长沙万象城汽车体验店</t>
+          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13192,7 +13192,7 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>桐兴巷与铜盆湖路交叉口西北160米 → 湖南省长沙市岳麓区桐兴巷与铜盆湖路交叉口西北160米</t>
+          <t>四川省遂宁市遂宁高新区物流港物流大道858-888号 → 四川省遂宁市遂宁高新区物流港主干道B南侧858-888号</t>
         </is>
       </c>
     </row>
@@ -13204,17 +13204,17 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13224,7 +13224,7 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>繁华大道29华天大厦向东20米3号整栋标准厂房 → 安徽省合肥市包河经济开发区繁华大道29华天大厦向东20米3号整栋标准厂房</t>
+          <t>青岛市市北区四流南路22号-8幢展厅 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心</t>
         </is>
       </c>
     </row>
@@ -13236,17 +13236,17 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车乐山天牛汽车城销售服务中心</t>
+          <t>小鹏汽车福州海盛汽车城交付中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车乐山天牛汽车城销售服务中心</t>
+          <t>小鹏汽车福州海盛汽车城交付中心</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13256,7 +13256,7 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>四川省乐山市市中区龙游路北段518号 → 四川省乐山市市中区龙游路北段518号1幢</t>
+          <t>福州市闽侯县荆溪镇永丰村洪甘路189号海盛汽车城 → 荆溪镇永丰村杜坞42号海盛汽车城A区5栋1层小鹏福州海盛交付中心</t>
         </is>
       </c>
     </row>
@@ -13268,17 +13268,17 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州海盛汽车城交付中心</t>
+          <t>小鹏汽车乐山天牛汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州海盛汽车城交付中心</t>
+          <t>小鹏汽车乐山天牛汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13288,7 +13288,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>福州市闽侯县荆溪镇永丰村洪甘路189号海盛汽车城 → 荆溪镇永丰村杜坞42号海盛汽车城A区5栋1层小鹏福州海盛交付中心</t>
+          <t>四川省乐山市市中区龙游路北段518号 → 四川省乐山市市中区龙游路北段518号1幢</t>
         </is>
       </c>
     </row>
@@ -13300,17 +13300,17 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津北辰双江道销售服务中心</t>
+          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津北辰双江道销售服务中心</t>
+          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13320,29 +13320,29 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>天津市北辰区双街镇庞大汽贸园原五菱宝骏店展厅 → 天津市北辰区双街镇庞大汽贸园原五菱骏宝店展厅</t>
+          <t>繁华大道29华天大厦向东20米3号整栋标准厂房 → 安徽省合肥市包河经济开发区繁华大道29华天大厦向东20米3号整栋标准厂房</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>昆明经开特斯拉中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>昆明经开特斯拉中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13352,7 +13352,7 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区四流南路22号-8幢展厅 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心</t>
+          <t>云南省昆明市自由贸易试验区昆明片区经开区出口加工区A6-1-2号（宝泽路41号）2栋 → 云南省昆明市经济开发区宝泽路41号2栋</t>
         </is>
       </c>
     </row>
@@ -13364,17 +13364,17 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保山联通汽车城销售中心</t>
+          <t>小鹏汽车常州金坛汽车城销售中心</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保山联通汽车城销售展厅</t>
+          <t>小鹏汽车常州金坛汽车城销售展厅</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -13384,7 +13384,7 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保山联通汽车城销售中心 → 小鹏汽车保山联通汽车城销售展厅</t>
+          <t>小鹏汽车常州金坛汽车城销售中心 → 小鹏汽车常州金坛汽车城销售展厅</t>
         </is>
       </c>
     </row>
@@ -13396,17 +13396,17 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常州金坛汽车城销售中心</t>
+          <t>小鹏汽车保山联通汽车城销售中心</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常州金坛汽车城销售展厅</t>
+          <t>小鹏汽车保山联通汽车城销售展厅</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -13416,7 +13416,7 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常州金坛汽车城销售中心 → 小鹏汽车常州金坛汽车城销售展厅</t>
+          <t>小鹏汽车保山联通汽车城销售中心 → 小鹏汽车保山联通汽车城销售展厅</t>
         </is>
       </c>
     </row>
@@ -13455,22 +13455,22 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海临港万达广场销售中心</t>
+          <t>宾利北京亦庄</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海临港万达销售展厅</t>
+          <t>宾利北京五棵松（新）</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -13492,17 +13492,17 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>深圳光明蓝鲸世界体验店L1-07/08</t>
+          <t>上海松江万达</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>深圳光明蓝鲸世界体验店</t>
+          <t>上海松江万达广场</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -13524,17 +13524,17 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>上海松江万达</t>
+          <t>深圳光明蓝鲸世界体验店L1-07/08</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>上海松江万达广场</t>
+          <t>深圳光明蓝鲸世界体验店</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -13551,22 +13551,22 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>宾利北京亦庄</t>
+          <t>华为智能生活馆•佛山岭南新天地</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>宾利北京五棵松（新）</t>
+          <t>华为智能生活馆•佛山岭南天地</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -13583,22 +13583,22 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•佛山岭南新天地</t>
+          <t>小鹏汽车上海临港万达广场销售中心</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•佛山岭南天地</t>
+          <t>小鹏汽车上海临港万达销售展厅</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260601_vs_20260608.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260601_vs_20260608.xlsx
@@ -12478,7 +12478,7 @@
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>华为智能生活馆•西宁王府井百货</t>
+          <t>华为智能生活馆•西宁海湖万达</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
@@ -12493,7 +12493,7 @@
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>青海省西宁市城中区西大街王府井百货B馆</t>
+          <t>青海省西宁市城西区海湖新区西关大街海湖万达广场2号门左侧</t>
         </is>
       </c>
       <c r="F51" s="3" t="inlineStr">
@@ -12510,7 +12510,7 @@
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>华为智能生活馆•西宁海湖万达</t>
+          <t>华为智能生活馆•西宁王府井百货</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
@@ -12525,7 +12525,7 @@
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>青海省西宁市城西区海湖新区西关大街海湖万达广场2号门左侧</t>
+          <t>青海省西宁市城中区西大街王府井百货B馆</t>
         </is>
       </c>
       <c r="F52" s="3" t="inlineStr">
@@ -12596,17 +12596,17 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>小鹏汽车汕头龙湖销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>小鹏汽车汕头龙湖销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12616,7 +12616,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅 → 新疆伊宁市巴彦岱城投汽车产业园</t>
+          <t>广东省汕头市龙湖区汕汾路与淮河路交界处北侧 → 汕头市龙湖区汕汾路与淮河路交界处北侧之一（东侧）</t>
         </is>
       </c>
     </row>
@@ -12628,17 +12628,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津北辰双江道销售服务中心</t>
+          <t>小鹏汽车潍坊潍州路销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津北辰双江道销售服务中心</t>
+          <t>小鹏汽车潍坊潍州路销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12648,7 +12648,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>天津市北辰区双街镇庞大汽贸园原五菱宝骏店展厅 → 天津市北辰区双街镇庞大汽贸园原五菱骏宝店展厅</t>
+          <t>山东省潍坊市奎文区潍州路2800号 → 潍坊市奎文区金宝乐园南100米路西</t>
         </is>
       </c>
     </row>
@@ -12660,17 +12660,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>小鹏汽车深圳福保销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>小鹏汽车深圳福保销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12680,29 +12680,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>河北省张家口市经济技术开发区张宣公路西侧白云街1号 → 河北省张家口市经济技术开发区白云街1号万国汽配城后</t>
+          <t>深圳市福田保税区蓝花道6号诚联物流大厦1层 → 广东省深圳市福田区蓝花道6号城联物流大厦一层</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（东吴银泰）</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（东吴银泰）</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12712,7 +12712,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>浙江省湖州市吴兴区劳动路518号湖州东吴银泰城1F层【1001-A,1001-B,1002、1-39】号 → 湖州市吴兴区劳动路518号湖州东吴银泰城1F层C馆（1001-A,1001-B,1002-C) 华为授权体验店</t>
+          <t>佛山市禅城区南庄镇醒群社村工业区5号 → 广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号</t>
         </is>
       </c>
     </row>
@@ -12724,17 +12724,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕头龙湖销售服务中心</t>
+          <t>小鹏汽车天津北辰双江道销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕头龙湖销售服务中心</t>
+          <t>小鹏汽车天津北辰双江道销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12744,29 +12744,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>广东省汕头市龙湖区汕汾路与淮河路交界处北侧 → 汕头市龙湖区汕汾路与淮河路交界处北侧之一（东侧）</t>
+          <t>天津市北辰区双街镇庞大汽贸园原五菱宝骏店展厅 → 天津市北辰区双街镇庞大汽贸园原五菱骏宝店展厅</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小米之家湖南省长沙市岳麓区长沙万象城汽车体验店</t>
+          <t>小鹏汽车福州海盛汽车城交付中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小米之家湖南省长沙市岳麓区长沙万象城汽车体验店</t>
+          <t>小鹏汽车福州海盛汽车城交付中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12776,7 +12776,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>桐兴巷与铜盆湖路交叉口西北160米 → 湖南省长沙市岳麓区桐兴巷与铜盆湖路交叉口西北160米</t>
+          <t>福州市闽侯县荆溪镇永丰村洪甘路189号海盛汽车城 → 荆溪镇永丰村杜坞42号海盛汽车城A区5栋1层小鹏福州海盛交付中心</t>
         </is>
       </c>
     </row>
@@ -12788,17 +12788,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊潍州路销售服务中心</t>
+          <t>小鹏汽车文山国际汽车城销售中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊潍州路销售服务中心</t>
+          <t>小鹏汽车文山国际汽车城销售中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12808,7 +12808,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>山东省潍坊市奎文区潍州路2800号 → 潍坊市奎文区金宝乐园南100米路西</t>
+          <t>云南省文山壮族苗族自治州文山市腾龙北路世纪名苑二期 → 云南省文山壮族苗族自治州文山市腾龙北路世纪名苑B期第28-31号商铺</t>
         </is>
       </c>
     </row>
@@ -12820,17 +12820,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>广州市锦龙汽车发展有限公司</t>
+          <t>上海德辰汽车销售有限公司</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>广州市锦龙汽车发展有限公司</t>
+          <t>上海德辰汽车销售有限公司</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12840,29 +12840,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>广东省广州市天河区广东省广州市天河区黄村街道奥体路55号(奥林匹克体育中心东门对面) → 广东省广州市天河区奥体南路5号</t>
+          <t>上海市闵行区颛兴东路1280弄3号(都会路口) → 上海市闵行区莲花南路2333号</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12872,7 +12872,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>龙跃街9号院 顺义区马坡聚源工业园 101317 → 新东路幸福二村40号楼 朝阳区 100027</t>
+          <t>青岛市市北区四流南路22号-8幢展厅 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心</t>
         </is>
       </c>
     </row>
@@ -12884,17 +12884,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海口南海大道销售服务中心</t>
+          <t>小鹏汽车北京五方天雅销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海口南海大道销售服务中心</t>
+          <t>小鹏汽车北京五方天雅销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12904,7 +12904,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>海南省海口市龙华区南海大道115号福德汽车城小鹏汽车 → 海南省海口市龙华区南海大道115号</t>
+          <t>北京市朝阳区王四营乡五方天雅B区B1-03 → 北京市朝阳区五方桥西南侧五方天雅市场内B区B1-03号</t>
         </is>
       </c>
     </row>
@@ -12948,17 +12948,17 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆万象城销售中心</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆万象城销售中心</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12968,29 +12968,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>重庆市九龙坡区万象城北区 → 重庆市九龙坡区万象城北区3号门NL132</t>
+          <t>新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅 → 新疆伊宁市巴彦岱城投汽车产业园</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳福保销售服务中心</t>
+          <t>华为授权体验店（东吴银泰）</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳福保销售服务中心</t>
+          <t>华为授权体验店（东吴银泰）</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -13000,7 +13000,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>深圳市福田保税区蓝花道6号诚联物流大厦1层 → 广东省深圳市福田区蓝花道6号城联物流大厦一层</t>
+          <t>浙江省湖州市吴兴区劳动路518号湖州东吴银泰城1F层【1001-A,1001-B,1002、1-39】号 → 湖州市吴兴区劳动路518号湖州东吴银泰城1F层C馆（1001-A,1001-B,1002-C) 华为授权体验店</t>
         </is>
       </c>
     </row>
@@ -13012,17 +13012,17 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车文山国际汽车城销售中心</t>
+          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车文山国际汽车城销售中心</t>
+          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -13032,14 +13032,14 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>云南省文山壮族苗族自治州文山市腾龙北路世纪名苑二期 → 云南省文山壮族苗族自治州文山市腾龙北路世纪名苑B期第28-31号商铺</t>
+          <t>繁华大道29华天大厦向东20米3号整栋标准厂房 → 安徽省合肥市包河经济开发区繁华大道29华天大厦向东20米3号整栋标准厂房</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
@@ -13049,12 +13049,12 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>广州市锦龙汽车发展有限公司</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>广州市锦龙汽车发展有限公司</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -13064,29 +13064,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>佛山市禅城区南庄镇醒群社村工业区5号 → 广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号</t>
+          <t>广东省广州市天河区广东省广州市天河区黄村街道奥体路55号(奥林匹克体育中心东门对面) → 广东省广州市天河区奥体南路5号</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>上海德辰汽车销售有限公司</t>
+          <t>小鹏汽车重庆万象城销售中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>上海德辰汽车销售有限公司</t>
+          <t>小鹏汽车重庆万象城销售中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13096,7 +13096,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>上海市闵行区颛兴东路1280弄3号(都会路口) → 上海市闵行区莲花南路2333号</t>
+          <t>重庆市九龙坡区万象城北区 → 重庆市九龙坡区万象城北区3号门NL132</t>
         </is>
       </c>
     </row>
@@ -13135,22 +13135,22 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京五方天雅销售服务中心</t>
+          <t>小米之家湖南省长沙市岳麓区长沙万象城汽车体验店</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京五方天雅销售服务中心</t>
+          <t>小米之家湖南省长沙市岳麓区长沙万象城汽车体验店</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13160,7 +13160,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>北京市朝阳区王四营乡五方天雅B区B1-03 → 北京市朝阳区五方桥西南侧五方天雅市场内B区B1-03号</t>
+          <t>桐兴巷与铜盆湖路交叉口西北160米 → 湖南省长沙市岳麓区桐兴巷与铜盆湖路交叉口西北160米</t>
         </is>
       </c>
     </row>
@@ -13177,12 +13177,12 @@
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
+          <t>小鹏汽车乐山天牛汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
+          <t>小鹏汽车乐山天牛汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13192,29 +13192,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>四川省遂宁市遂宁高新区物流港物流大道858-888号 → 四川省遂宁市遂宁高新区物流港主干道B南侧858-888号</t>
+          <t>四川省乐山市市中区龙游路北段518号 → 四川省乐山市市中区龙游路北段518号1幢</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>昆明经开特斯拉中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>昆明经开特斯拉中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13224,7 +13224,7 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区四流南路22号-8幢展厅 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心</t>
+          <t>云南省昆明市自由贸易试验区昆明片区经开区出口加工区A6-1-2号（宝泽路41号）2栋 → 云南省昆明市经济开发区宝泽路41号2栋</t>
         </is>
       </c>
     </row>
@@ -13236,17 +13236,17 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州海盛汽车城交付中心</t>
+          <t>小鹏汽车海口南海大道销售服务中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州海盛汽车城交付中心</t>
+          <t>小鹏汽车海口南海大道销售服务中心</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13256,29 +13256,29 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>福州市闽侯县荆溪镇永丰村洪甘路189号海盛汽车城 → 荆溪镇永丰村杜坞42号海盛汽车城A区5栋1层小鹏福州海盛交付中心</t>
+          <t>海南省海口市龙华区南海大道115号福德汽车城小鹏汽车 → 海南省海口市龙华区南海大道115号</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车乐山天牛汽车城销售服务中心</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车乐山天牛汽车城销售服务中心</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13288,7 +13288,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>四川省乐山市市中区龙游路北段518号 → 四川省乐山市市中区龙游路北段518号1幢</t>
+          <t>龙跃街9号院 顺义区马坡聚源工业园 101317 → 新东路幸福二村40号楼 朝阳区 100027</t>
         </is>
       </c>
     </row>
@@ -13300,17 +13300,17 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
+          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
+          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13320,29 +13320,29 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>繁华大道29华天大厦向东20米3号整栋标准厂房 → 安徽省合肥市包河经济开发区繁华大道29华天大厦向东20米3号整栋标准厂房</t>
+          <t>四川省遂宁市遂宁高新区物流港物流大道858-888号 → 四川省遂宁市遂宁高新区物流港主干道B南侧858-888号</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>昆明经开特斯拉中心</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>昆明经开特斯拉中心</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13352,7 +13352,7 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>云南省昆明市自由贸易试验区昆明片区经开区出口加工区A6-1-2号（宝泽路41号）2栋 → 云南省昆明市经济开发区宝泽路41号2栋</t>
+          <t>河北省张家口市经济技术开发区张宣公路西侧白云街1号 → 河北省张家口市经济技术开发区白云街1号万国汽配城后</t>
         </is>
       </c>
     </row>
@@ -13423,22 +13423,22 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>宾利北京亦庄</t>
+          <t>上海松江万达</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>宾利北京五棵松（新）</t>
+          <t>上海松江万达广场</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -13455,22 +13455,22 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>宾利北京亦庄</t>
+          <t>小鹏汽车上海临港万达广场销售中心</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>宾利北京五棵松（新）</t>
+          <t>小鹏汽车上海临港万达销售展厅</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -13487,22 +13487,22 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>上海松江万达</t>
+          <t>宾利北京亦庄</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>上海松江万达广场</t>
+          <t>宾利北京五棵松（新）</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -13519,22 +13519,22 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>深圳光明蓝鲸世界体验店L1-07/08</t>
+          <t>宾利北京亦庄</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>深圳光明蓝鲸世界体验店</t>
+          <t>宾利北京五棵松（新）</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -13551,7 +13551,7 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
@@ -13561,12 +13561,12 @@
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•佛山岭南新天地</t>
+          <t>深圳光明蓝鲸世界体验店L1-07/08</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•佛山岭南天地</t>
+          <t>深圳光明蓝鲸世界体验店</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -13583,22 +13583,22 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海临港万达广场销售中心</t>
+          <t>华为智能生活馆•佛山岭南新天地</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海临港万达销售展厅</t>
+          <t>华为智能生活馆•佛山岭南天地</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -13652,17 +13652,17 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•蚌埠银泰</t>
+          <t>华为授权体验店（融创广场）</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•蚌埠银泰城</t>
+          <t>华为授权体验店（永旺梦乐城）</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -13672,7 +13672,7 @@
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 96%</t>
+          <t>店名相似度 100%</t>
         </is>
       </c>
     </row>
@@ -13684,17 +13684,17 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（融创广场）</t>
+          <t>华为智能生活馆•蚌埠银泰</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（永旺梦乐城）</t>
+          <t>华为智能生活馆•蚌埠银泰城</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -13704,7 +13704,7 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 100%</t>
+          <t>店名相似度 96%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260601_vs_20260608.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260601_vs_20260608.xlsx
@@ -11518,7 +11518,7 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉江夏永旺销售中心</t>
+          <t>小鹏汽车武汉江宸龙湖天街销售中心</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
@@ -11533,12 +11533,12 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>湖北省武汉市江夏区文化大道199号永旺梦乐城1F-1062-2</t>
+          <t>湖北省武汉市江汉区青年路518号江宸龙湖天街负一楼小鹏汽车体验中心</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>连续在档 5 期；本期存在高相似店名「小鹏汽车武汉经开永旺销售中心」（疑似改名/合并，非真实关店）</t>
+          <t>连续在档 5 期</t>
         </is>
       </c>
     </row>
@@ -11550,7 +11550,7 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉江宸龙湖天街销售中心</t>
+          <t>小鹏汽车武汉江夏永旺销售中心</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
@@ -11565,12 +11565,12 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>湖北省武汉市江汉区青年路518号江宸龙湖天街负一楼小鹏汽车体验中心</t>
+          <t>湖北省武汉市江夏区文化大道199号永旺梦乐城1F-1062-2</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>连续在档 5 期</t>
+          <t>连续在档 5 期；本期存在高相似店名「小鹏汽车武汉经开永旺销售中心」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -11582,7 +11582,7 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>小鹏汽车西安芙蓉新天地销售中心</t>
+          <t>小鹏汽车西安王府井销售中心</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
@@ -11597,7 +11597,7 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>西安市曲江新区芙蓉南路芙蓉新天地购物中心1F-F1005</t>
+          <t>陕西省西安市未央区未央路170号熙地港负一层王府井新能源展厅</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
@@ -11614,7 +11614,7 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>小鹏汽车西安王府井销售中心</t>
+          <t>小鹏汽车西安芙蓉新天地销售中心</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -11629,7 +11629,7 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>陕西省西安市未央区未央路170号熙地港负一层王府井新能源展厅</t>
+          <t>西安市曲江新区芙蓉南路芙蓉新天地购物中心1F-F1005</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
@@ -12446,7 +12446,7 @@
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>华为智能生活馆•西宁城东吾悦</t>
+          <t>华为智能生活馆•西宁王府井百货</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
@@ -12461,7 +12461,7 @@
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>青海省西宁市城东区八一路与民和路交叉口东南西宁城东吾悦广场</t>
+          <t>青海省西宁市城中区西大街王府井百货B馆</t>
         </is>
       </c>
       <c r="F50" s="3" t="inlineStr">
@@ -12510,7 +12510,7 @@
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>华为智能生活馆•西宁王府井百货</t>
+          <t>华为智能生活馆•西宁城东吾悦</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
@@ -12525,7 +12525,7 @@
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>青海省西宁市城中区西大街王府井百货B馆</t>
+          <t>青海省西宁市城东区八一路与民和路交叉口东南西宁城东吾悦广场</t>
         </is>
       </c>
       <c r="F52" s="3" t="inlineStr">
@@ -12601,12 +12601,12 @@
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕头龙湖销售服务中心</t>
+          <t>小鹏汽车深圳福保销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕头龙湖销售服务中心</t>
+          <t>小鹏汽车深圳福保销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12616,29 +12616,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>广东省汕头市龙湖区汕汾路与淮河路交界处北侧 → 汕头市龙湖区汕汾路与淮河路交界处北侧之一（东侧）</t>
+          <t>深圳市福田保税区蓝花道6号诚联物流大厦1层 → 广东省深圳市福田区蓝花道6号城联物流大厦一层</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊潍州路销售服务中心</t>
+          <t>上海德辰汽车销售有限公司</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊潍州路销售服务中心</t>
+          <t>上海德辰汽车销售有限公司</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12648,7 +12648,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>山东省潍坊市奎文区潍州路2800号 → 潍坊市奎文区金宝乐园南100米路西</t>
+          <t>上海市闵行区颛兴东路1280弄3号(都会路口) → 上海市闵行区莲花南路2333号</t>
         </is>
       </c>
     </row>
@@ -12660,17 +12660,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳福保销售服务中心</t>
+          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳福保销售服务中心</t>
+          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12680,7 +12680,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>深圳市福田保税区蓝花道6号诚联物流大厦1层 → 广东省深圳市福田区蓝花道6号城联物流大厦一层</t>
+          <t>繁华大道29华天大厦向东20米3号整栋标准厂房 → 安徽省合肥市包河经济开发区繁华大道29华天大厦向东20米3号整栋标准厂房</t>
         </is>
       </c>
     </row>
@@ -12692,17 +12692,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>小鹏汽车北京五方天雅销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>小鹏汽车北京五方天雅销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12712,29 +12712,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>佛山市禅城区南庄镇醒群社村工业区5号 → 广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号</t>
+          <t>北京市朝阳区王四营乡五方天雅B区B1-03 → 北京市朝阳区五方桥西南侧五方天雅市场内B区B1-03号</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津北辰双江道销售服务中心</t>
+          <t>小米之家湖南省长沙市岳麓区长沙万象城汽车体验店</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津北辰双江道销售服务中心</t>
+          <t>小米之家湖南省长沙市岳麓区长沙万象城汽车体验店</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12744,7 +12744,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>天津市北辰区双街镇庞大汽贸园原五菱宝骏店展厅 → 天津市北辰区双街镇庞大汽贸园原五菱骏宝店展厅</t>
+          <t>桐兴巷与铜盆湖路交叉口西北160米 → 湖南省长沙市岳麓区桐兴巷与铜盆湖路交叉口西北160米</t>
         </is>
       </c>
     </row>
@@ -12756,17 +12756,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州海盛汽车城交付中心</t>
+          <t>小鹏汽车文山国际汽车城销售中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州海盛汽车城交付中心</t>
+          <t>小鹏汽车文山国际汽车城销售中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12776,29 +12776,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>福州市闽侯县荆溪镇永丰村洪甘路189号海盛汽车城 → 荆溪镇永丰村杜坞42号海盛汽车城A区5栋1层小鹏福州海盛交付中心</t>
+          <t>云南省文山壮族苗族自治州文山市腾龙北路世纪名苑二期 → 云南省文山壮族苗族自治州文山市腾龙北路世纪名苑B期第28-31号商铺</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车文山国际汽车城销售中心</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车文山国际汽车城销售中心</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12808,29 +12808,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>云南省文山壮族苗族自治州文山市腾龙北路世纪名苑二期 → 云南省文山壮族苗族自治州文山市腾龙北路世纪名苑B期第28-31号商铺</t>
+          <t>龙跃街9号院 顺义区马坡聚源工业园 101317 → 新东路幸福二村40号楼 朝阳区 100027</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>上海德辰汽车销售有限公司</t>
+          <t>小鹏汽车重庆万象城销售中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>上海德辰汽车销售有限公司</t>
+          <t>小鹏汽车重庆万象城销售中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12840,29 +12840,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>上海市闵行区颛兴东路1280弄3号(都会路口) → 上海市闵行区莲花南路2333号</t>
+          <t>重庆市九龙坡区万象城北区 → 重庆市九龙坡区万象城北区3号门NL132</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>昆明经开特斯拉中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>昆明经开特斯拉中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12872,7 +12872,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区四流南路22号-8幢展厅 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心</t>
+          <t>云南省昆明市自由贸易试验区昆明片区经开区出口加工区A6-1-2号（宝泽路41号）2栋 → 云南省昆明市经济开发区宝泽路41号2栋</t>
         </is>
       </c>
     </row>
@@ -12884,17 +12884,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京五方天雅销售服务中心</t>
+          <t>小鹏汽车天津北辰双江道销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京五方天雅销售服务中心</t>
+          <t>小鹏汽车天津北辰双江道销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12904,7 +12904,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>北京市朝阳区王四营乡五方天雅B区B1-03 → 北京市朝阳区五方桥西南侧五方天雅市场内B区B1-03号</t>
+          <t>天津市北辰区双街镇庞大汽贸园原五菱宝骏店展厅 → 天津市北辰区双街镇庞大汽贸园原五菱骏宝店展厅</t>
         </is>
       </c>
     </row>
@@ -12921,12 +12921,12 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州龙溪大道销售服务中心</t>
+          <t>小鹏汽车汕头龙湖销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州龙溪大道销售服务中心</t>
+          <t>小鹏汽车汕头龙湖销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12936,7 +12936,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>广东省广州市荔湾区龙溪大道488号场内自编号为86号 → 广东省广州市荔湾区龙溪大道488号金马汽车交易城小鹏汽车</t>
+          <t>广东省汕头市龙湖区汕汾路与淮河路交界处北侧 → 汕头市龙湖区汕汾路与淮河路交界处北侧之一（东侧）</t>
         </is>
       </c>
     </row>
@@ -12948,17 +12948,17 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12968,7 +12968,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅 → 新疆伊宁市巴彦岱城投汽车产业园</t>
+          <t>青岛市市北区四流南路22号-8幢展厅 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心</t>
         </is>
       </c>
     </row>
@@ -13012,17 +13012,17 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
+          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
+          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -13032,29 +13032,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>繁华大道29华天大厦向东20米3号整栋标准厂房 → 安徽省合肥市包河经济开发区繁华大道29华天大厦向东20米3号整栋标准厂房</t>
+          <t>四川省遂宁市遂宁高新区物流港物流大道858-888号 → 四川省遂宁市遂宁高新区物流港主干道B南侧858-888号</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>广州市锦龙汽车发展有限公司</t>
+          <t>小鹏汽车福州海盛汽车城交付中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>广州市锦龙汽车发展有限公司</t>
+          <t>小鹏汽车福州海盛汽车城交付中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -13064,7 +13064,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>广东省广州市天河区广东省广州市天河区黄村街道奥体路55号(奥林匹克体育中心东门对面) → 广东省广州市天河区奥体南路5号</t>
+          <t>福州市闽侯县荆溪镇永丰村洪甘路189号海盛汽车城 → 荆溪镇永丰村杜坞42号海盛汽车城A区5栋1层小鹏福州海盛交付中心</t>
         </is>
       </c>
     </row>
@@ -13076,17 +13076,17 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆万象城销售中心</t>
+          <t>小鹏汽车乐山天牛汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆万象城销售中心</t>
+          <t>小鹏汽车乐山天牛汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13096,7 +13096,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>重庆市九龙坡区万象城北区 → 重庆市九龙坡区万象城北区3号门NL132</t>
+          <t>四川省乐山市市中区龙游路北段518号 → 四川省乐山市市中区龙游路北段518号1幢</t>
         </is>
       </c>
     </row>
@@ -13108,17 +13108,17 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小鹏汽车潍坊潍州路销售服务中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小鹏汽车潍坊潍州路销售服务中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13128,29 +13128,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
+          <t>山东省潍坊市奎文区潍州路2800号 → 潍坊市奎文区金宝乐园南100米路西</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小米之家湖南省长沙市岳麓区长沙万象城汽车体验店</t>
+          <t>广州市锦龙汽车发展有限公司</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小米之家湖南省长沙市岳麓区长沙万象城汽车体验店</t>
+          <t>广州市锦龙汽车发展有限公司</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13160,7 +13160,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>桐兴巷与铜盆湖路交叉口西北160米 → 湖南省长沙市岳麓区桐兴巷与铜盆湖路交叉口西北160米</t>
+          <t>广东省广州市天河区广东省广州市天河区黄村街道奥体路55号(奥林匹克体育中心东门对面) → 广东省广州市天河区奥体南路5号</t>
         </is>
       </c>
     </row>
@@ -13172,17 +13172,17 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车乐山天牛汽车城销售服务中心</t>
+          <t>小鹏汽车广州龙溪大道销售服务中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车乐山天牛汽车城销售服务中心</t>
+          <t>小鹏汽车广州龙溪大道销售服务中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13192,29 +13192,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>四川省乐山市市中区龙游路北段518号 → 四川省乐山市市中区龙游路北段518号1幢</t>
+          <t>广东省广州市荔湾区龙溪大道488号场内自编号为86号 → 广东省广州市荔湾区龙溪大道488号金马汽车交易城小鹏汽车</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>昆明经开特斯拉中心</t>
+          <t>小鹏汽车海口南海大道销售服务中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>昆明经开特斯拉中心</t>
+          <t>小鹏汽车海口南海大道销售服务中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13224,7 +13224,7 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>云南省昆明市自由贸易试验区昆明片区经开区出口加工区A6-1-2号（宝泽路41号）2栋 → 云南省昆明市经济开发区宝泽路41号2栋</t>
+          <t>海南省海口市龙华区南海大道115号福德汽车城小鹏汽车 → 海南省海口市龙华区南海大道115号</t>
         </is>
       </c>
     </row>
@@ -13236,17 +13236,17 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海口南海大道销售服务中心</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海口南海大道销售服务中心</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13256,29 +13256,29 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>海南省海口市龙华区南海大道115号福德汽车城小鹏汽车 → 海南省海口市龙华区南海大道115号</t>
+          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13288,7 +13288,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>龙跃街9号院 顺义区马坡聚源工业园 101317 → 新东路幸福二村40号楼 朝阳区 100027</t>
+          <t>佛山市禅城区南庄镇醒群社村工业区5号 → 广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号</t>
         </is>
       </c>
     </row>
@@ -13300,17 +13300,17 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13320,7 +13320,7 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>四川省遂宁市遂宁高新区物流港物流大道858-888号 → 四川省遂宁市遂宁高新区物流港主干道B南侧858-888号</t>
+          <t>河北省张家口市经济技术开发区张宣公路西侧白云街1号 → 河北省张家口市经济技术开发区白云街1号万国汽配城后</t>
         </is>
       </c>
     </row>
@@ -13332,17 +13332,17 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13352,7 +13352,7 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>河北省张家口市经济技术开发区张宣公路西侧白云街1号 → 河北省张家口市经济技术开发区白云街1号万国汽配城后</t>
+          <t>新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅 → 新疆伊宁市巴彦岱城投汽车产业园</t>
         </is>
       </c>
     </row>
@@ -13423,22 +13423,22 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>上海松江万达</t>
+          <t>宾利北京亦庄</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>上海松江万达广场</t>
+          <t>宾利北京五棵松（新）</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -13455,7 +13455,7 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
@@ -13465,12 +13465,12 @@
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海临港万达广场销售中心</t>
+          <t>上海松江万达</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海临港万达销售展厅</t>
+          <t>上海松江万达广场</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -13487,22 +13487,22 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>宾利北京亦庄</t>
+          <t>华为智能生活馆•佛山岭南新天地</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>宾利北京五棵松（新）</t>
+          <t>华为智能生活馆•佛山岭南天地</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -13524,7 +13524,7 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
@@ -13551,22 +13551,22 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>深圳光明蓝鲸世界体验店L1-07/08</t>
+          <t>小鹏汽车上海临港万达广场销售中心</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>深圳光明蓝鲸世界体验店</t>
+          <t>小鹏汽车上海临港万达销售展厅</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -13583,7 +13583,7 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
@@ -13593,12 +13593,12 @@
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•佛山岭南新天地</t>
+          <t>深圳光明蓝鲸世界体验店L1-07/08</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•佛山岭南天地</t>
+          <t>深圳光明蓝鲸世界体验店</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -13652,17 +13652,17 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（融创广场）</t>
+          <t>华为智能生活馆•蚌埠银泰</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（永旺梦乐城）</t>
+          <t>华为智能生活馆•蚌埠银泰城</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -13672,7 +13672,7 @@
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 100%</t>
+          <t>店名相似度 96%</t>
         </is>
       </c>
     </row>
@@ -13684,17 +13684,17 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•蚌埠银泰</t>
+          <t>华为授权体验店（融创广场）</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•蚌埠银泰城</t>
+          <t>华为授权体验店（永旺梦乐城）</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -13704,7 +13704,7 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 96%</t>
+          <t>店名相似度 100%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260601_vs_20260608.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260601_vs_20260608.xlsx
@@ -11518,7 +11518,7 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉江宸龙湖天街销售中心</t>
+          <t>小鹏汽车武汉江夏永旺销售中心</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
@@ -11533,12 +11533,12 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>湖北省武汉市江汉区青年路518号江宸龙湖天街负一楼小鹏汽车体验中心</t>
+          <t>湖北省武汉市江夏区文化大道199号永旺梦乐城1F-1062-2</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>连续在档 5 期</t>
+          <t>连续在档 5 期；本期存在高相似店名「小鹏汽车武汉经开永旺销售中心」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -11550,7 +11550,7 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉江夏永旺销售中心</t>
+          <t>小鹏汽车武汉江宸龙湖天街销售中心</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
@@ -11565,12 +11565,12 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>湖北省武汉市江夏区文化大道199号永旺梦乐城1F-1062-2</t>
+          <t>湖北省武汉市江汉区青年路518号江宸龙湖天街负一楼小鹏汽车体验中心</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>连续在档 5 期；本期存在高相似店名「小鹏汽车武汉经开永旺销售中心」（疑似改名/合并，非真实关店）</t>
+          <t>连续在档 5 期</t>
         </is>
       </c>
     </row>
@@ -11582,7 +11582,7 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>小鹏汽车西安王府井销售中心</t>
+          <t>小鹏汽车西安芙蓉新天地销售中心</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
@@ -11597,7 +11597,7 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>陕西省西安市未央区未央路170号熙地港负一层王府井新能源展厅</t>
+          <t>西安市曲江新区芙蓉南路芙蓉新天地购物中心1F-F1005</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
@@ -11614,7 +11614,7 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>小鹏汽车西安芙蓉新天地销售中心</t>
+          <t>小鹏汽车西安王府井销售中心</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -11629,7 +11629,7 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>西安市曲江新区芙蓉南路芙蓉新天地购物中心1F-F1005</t>
+          <t>陕西省西安市未央区未央路170号熙地港负一层王府井新能源展厅</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
@@ -12094,7 +12094,7 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>华为授权体验店（相城龙湖）</t>
+          <t>华为授权体验店（融创广场）</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
@@ -12104,12 +12104,12 @@
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>苏州市</t>
+          <t>淮安市</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>江苏省苏州市相城区相城大道1399号龙湖天街一层A1F-25、26号</t>
+          <t xml:space="preserve"> 江苏省淮安市清江浦区天津路融创广场一楼华为</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
@@ -12318,7 +12318,7 @@
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•贵阳通源云岩</t>
+          <t>AITO授权用户中心•贵阳观山湖通源汽车文化广场</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
@@ -12333,7 +12333,7 @@
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>贵州省贵阳市云岩区新添大道南段485号</t>
+          <t>贵州省贵阳市观山湖区林城西路通源汽车文化广场一号钻石厅1楼</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
@@ -12350,7 +12350,7 @@
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•贵阳观山湖通源汽车文化广场</t>
+          <t>AITO授权用户中心•贵阳通源云岩</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
@@ -12365,7 +12365,7 @@
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>贵州省贵阳市观山湖区林城西路通源汽车文化广场一号钻石厅1楼</t>
+          <t>贵州省贵阳市云岩区新添大道南段485号</t>
         </is>
       </c>
       <c r="F47" s="3" t="inlineStr">
@@ -12446,7 +12446,7 @@
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>华为智能生活馆•西宁王府井百货</t>
+          <t>华为智能生活馆•西宁城东吾悦</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
@@ -12461,7 +12461,7 @@
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>青海省西宁市城中区西大街王府井百货B馆</t>
+          <t>青海省西宁市城东区八一路与民和路交叉口东南西宁城东吾悦广场</t>
         </is>
       </c>
       <c r="F50" s="3" t="inlineStr">
@@ -12478,7 +12478,7 @@
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>华为智能生活馆•西宁海湖万达</t>
+          <t>华为智能生活馆•西宁王府井百货</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
@@ -12493,7 +12493,7 @@
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>青海省西宁市城西区海湖新区西关大街海湖万达广场2号门左侧</t>
+          <t>青海省西宁市城中区西大街王府井百货B馆</t>
         </is>
       </c>
       <c r="F51" s="3" t="inlineStr">
@@ -12510,7 +12510,7 @@
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>华为智能生活馆•西宁城东吾悦</t>
+          <t>华为智能生活馆•西宁海湖万达</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
@@ -12525,7 +12525,7 @@
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>青海省西宁市城东区八一路与民和路交叉口东南西宁城东吾悦广场</t>
+          <t>青海省西宁市城西区海湖新区西关大街海湖万达广场2号门左侧</t>
         </is>
       </c>
       <c r="F52" s="3" t="inlineStr">
@@ -12596,17 +12596,17 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳福保销售服务中心</t>
+          <t>小鹏汽车乐山天牛汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳福保销售服务中心</t>
+          <t>小鹏汽车乐山天牛汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12616,7 +12616,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>深圳市福田保税区蓝花道6号诚联物流大厦1层 → 广东省深圳市福田区蓝花道6号城联物流大厦一层</t>
+          <t>四川省乐山市市中区龙游路北段518号 → 四川省乐山市市中区龙游路北段518号1幢</t>
         </is>
       </c>
     </row>
@@ -12660,17 +12660,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
+          <t>小鹏汽车福州海盛汽车城交付中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
+          <t>小鹏汽车福州海盛汽车城交付中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12680,29 +12680,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>繁华大道29华天大厦向东20米3号整栋标准厂房 → 安徽省合肥市包河经济开发区繁华大道29华天大厦向东20米3号整栋标准厂房</t>
+          <t>福州市闽侯县荆溪镇永丰村洪甘路189号海盛汽车城 → 荆溪镇永丰村杜坞42号海盛汽车城A区5栋1层小鹏福州海盛交付中心</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京五方天雅销售服务中心</t>
+          <t>小米之家湖南省长沙市岳麓区长沙万象城汽车体验店</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京五方天雅销售服务中心</t>
+          <t>小米之家湖南省长沙市岳麓区长沙万象城汽车体验店</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12712,29 +12712,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>北京市朝阳区王四营乡五方天雅B区B1-03 → 北京市朝阳区五方桥西南侧五方天雅市场内B区B1-03号</t>
+          <t>桐兴巷与铜盆湖路交叉口西北160米 → 湖南省长沙市岳麓区桐兴巷与铜盆湖路交叉口西北160米</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小米之家湖南省长沙市岳麓区长沙万象城汽车体验店</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小米之家湖南省长沙市岳麓区长沙万象城汽车体验店</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12744,7 +12744,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>桐兴巷与铜盆湖路交叉口西北160米 → 湖南省长沙市岳麓区桐兴巷与铜盆湖路交叉口西北160米</t>
+          <t>龙跃街9号院 顺义区马坡聚源工业园 101317 → 新东路幸福二村40号楼 朝阳区 100027</t>
         </is>
       </c>
     </row>
@@ -12756,17 +12756,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车文山国际汽车城销售中心</t>
+          <t>小鹏汽车天津北辰双江道销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车文山国际汽车城销售中心</t>
+          <t>小鹏汽车天津北辰双江道销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12776,29 +12776,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>云南省文山壮族苗族自治州文山市腾龙北路世纪名苑二期 → 云南省文山壮族苗族自治州文山市腾龙北路世纪名苑B期第28-31号商铺</t>
+          <t>天津市北辰区双街镇庞大汽贸园原五菱宝骏店展厅 → 天津市北辰区双街镇庞大汽贸园原五菱骏宝店展厅</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12808,7 +12808,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>龙跃街9号院 顺义区马坡聚源工业园 101317 → 新东路幸福二村40号楼 朝阳区 100027</t>
+          <t>河北省张家口市经济技术开发区张宣公路西侧白云街1号 → 河北省张家口市经济技术开发区白云街1号万国汽配城后</t>
         </is>
       </c>
     </row>
@@ -12820,17 +12820,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆万象城销售中心</t>
+          <t>小鹏汽车文山国际汽车城销售中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆万象城销售中心</t>
+          <t>小鹏汽车文山国际汽车城销售中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12840,7 +12840,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>重庆市九龙坡区万象城北区 → 重庆市九龙坡区万象城北区3号门NL132</t>
+          <t>云南省文山壮族苗族自治州文山市腾龙北路世纪名苑二期 → 云南省文山壮族苗族自治州文山市腾龙北路世纪名苑B期第28-31号商铺</t>
         </is>
       </c>
     </row>
@@ -12884,17 +12884,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津北辰双江道销售服务中心</t>
+          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津北辰双江道销售服务中心</t>
+          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12904,7 +12904,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>天津市北辰区双街镇庞大汽贸园原五菱宝骏店展厅 → 天津市北辰区双街镇庞大汽贸园原五菱骏宝店展厅</t>
+          <t>四川省遂宁市遂宁高新区物流港物流大道858-888号 → 四川省遂宁市遂宁高新区物流港主干道B南侧858-888号</t>
         </is>
       </c>
     </row>
@@ -12916,17 +12916,17 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕头龙湖销售服务中心</t>
+          <t>小鹏汽车北京五方天雅销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕头龙湖销售服务中心</t>
+          <t>小鹏汽车北京五方天雅销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12936,7 +12936,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>广东省汕头市龙湖区汕汾路与淮河路交界处北侧 → 汕头市龙湖区汕汾路与淮河路交界处北侧之一（东侧）</t>
+          <t>北京市朝阳区王四营乡五方天雅B区B1-03 → 北京市朝阳区五方桥西南侧五方天雅市场内B区B1-03号</t>
         </is>
       </c>
     </row>
@@ -12948,17 +12948,17 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12968,29 +12968,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区四流南路22号-8幢展厅 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心</t>
+          <t>繁华大道29华天大厦向东20米3号整栋标准厂房 → 安徽省合肥市包河经济开发区繁华大道29华天大厦向东20米3号整栋标准厂房</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（东吴银泰）</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（东吴银泰）</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -13000,29 +13000,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>浙江省湖州市吴兴区劳动路518号湖州东吴银泰城1F层【1001-A,1001-B,1002、1-39】号 → 湖州市吴兴区劳动路518号湖州东吴银泰城1F层C馆（1001-A,1001-B,1002-C) 华为授权体验店</t>
+          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
+          <t>广州市锦龙汽车发展有限公司</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
+          <t>广州市锦龙汽车发展有限公司</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -13032,29 +13032,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>四川省遂宁市遂宁高新区物流港物流大道858-888号 → 四川省遂宁市遂宁高新区物流港主干道B南侧858-888号</t>
+          <t>广东省广州市天河区广东省广州市天河区黄村街道奥体路55号(奥林匹克体育中心东门对面) → 广东省广州市天河区奥体南路5号</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州海盛汽车城交付中心</t>
+          <t>华为授权体验店（东吴银泰）</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州海盛汽车城交付中心</t>
+          <t>华为授权体验店（东吴银泰）</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -13064,7 +13064,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>福州市闽侯县荆溪镇永丰村洪甘路189号海盛汽车城 → 荆溪镇永丰村杜坞42号海盛汽车城A区5栋1层小鹏福州海盛交付中心</t>
+          <t>浙江省湖州市吴兴区劳动路518号湖州东吴银泰城1F层【1001-A,1001-B,1002、1-39】号 → 湖州市吴兴区劳动路518号湖州东吴银泰城1F层C馆（1001-A,1001-B,1002-C) 华为授权体验店</t>
         </is>
       </c>
     </row>
@@ -13076,17 +13076,17 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车乐山天牛汽车城销售服务中心</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车乐山天牛汽车城销售服务中心</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13096,7 +13096,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>四川省乐山市市中区龙游路北段518号 → 四川省乐山市市中区龙游路北段518号1幢</t>
+          <t>佛山市禅城区南庄镇醒群社村工业区5号 → 广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号</t>
         </is>
       </c>
     </row>
@@ -13108,17 +13108,17 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊潍州路销售服务中心</t>
+          <t>小鹏汽车重庆万象城销售中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊潍州路销售服务中心</t>
+          <t>小鹏汽车重庆万象城销售中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13128,29 +13128,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>山东省潍坊市奎文区潍州路2800号 → 潍坊市奎文区金宝乐园南100米路西</t>
+          <t>重庆市九龙坡区万象城北区 → 重庆市九龙坡区万象城北区3号门NL132</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>广州市锦龙汽车发展有限公司</t>
+          <t>小鹏汽车潍坊潍州路销售服务中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>广州市锦龙汽车发展有限公司</t>
+          <t>小鹏汽车潍坊潍州路销售服务中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13160,7 +13160,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>广东省广州市天河区广东省广州市天河区黄村街道奥体路55号(奥林匹克体育中心东门对面) → 广东省广州市天河区奥体南路5号</t>
+          <t>山东省潍坊市奎文区潍州路2800号 → 潍坊市奎文区金宝乐园南100米路西</t>
         </is>
       </c>
     </row>
@@ -13177,12 +13177,12 @@
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州龙溪大道销售服务中心</t>
+          <t>小鹏汽车深圳福保销售服务中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州龙溪大道销售服务中心</t>
+          <t>小鹏汽车深圳福保销售服务中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13192,7 +13192,7 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>广东省广州市荔湾区龙溪大道488号场内自编号为86号 → 广东省广州市荔湾区龙溪大道488号金马汽车交易城小鹏汽车</t>
+          <t>深圳市福田保税区蓝花道6号诚联物流大厦1层 → 广东省深圳市福田区蓝花道6号城联物流大厦一层</t>
         </is>
       </c>
     </row>
@@ -13236,17 +13236,17 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13256,7 +13256,7 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
+          <t>新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅 → 新疆伊宁市巴彦岱城投汽车产业园</t>
         </is>
       </c>
     </row>
@@ -13273,12 +13273,12 @@
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>小鹏汽车汕头龙湖销售服务中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>小鹏汽车汕头龙湖销售服务中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13288,7 +13288,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>佛山市禅城区南庄镇醒群社村工业区5号 → 广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号</t>
+          <t>广东省汕头市龙湖区汕汾路与淮河路交界处北侧 → 汕头市龙湖区汕汾路与淮河路交界处北侧之一（东侧）</t>
         </is>
       </c>
     </row>
@@ -13300,17 +13300,17 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13320,7 +13320,7 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>河北省张家口市经济技术开发区张宣公路西侧白云街1号 → 河北省张家口市经济技术开发区白云街1号万国汽配城后</t>
+          <t>青岛市市北区四流南路22号-8幢展厅 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心</t>
         </is>
       </c>
     </row>
@@ -13332,17 +13332,17 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>小鹏汽车广州龙溪大道销售服务中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>小鹏汽车广州龙溪大道销售服务中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13352,7 +13352,7 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅 → 新疆伊宁市巴彦岱城投汽车产业园</t>
+          <t>广东省广州市荔湾区龙溪大道488号场内自编号为86号 → 广东省广州市荔湾区龙溪大道488号金马汽车交易城小鹏汽车</t>
         </is>
       </c>
     </row>
@@ -13423,22 +13423,22 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>宾利北京亦庄</t>
+          <t>华为智能生活馆•佛山岭南新天地</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>宾利北京五棵松（新）</t>
+          <t>华为智能生活馆•佛山岭南天地</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -13487,7 +13487,7 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
@@ -13497,12 +13497,12 @@
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•佛山岭南新天地</t>
+          <t>深圳光明蓝鲸世界体验店L1-07/08</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•佛山岭南天地</t>
+          <t>深圳光明蓝鲸世界体验店</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -13551,22 +13551,22 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海临港万达广场销售中心</t>
+          <t>宾利北京亦庄</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海临港万达销售展厅</t>
+          <t>宾利北京五棵松（新）</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -13583,22 +13583,22 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>深圳光明蓝鲸世界体验店L1-07/08</t>
+          <t>小鹏汽车上海临港万达广场销售中心</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>深圳光明蓝鲸世界体验店</t>
+          <t>小鹏汽车上海临港万达销售展厅</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -13689,7 +13689,7 @@
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（融创广场）</t>
+          <t>华为授权体验店（相城龙湖）</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260601_vs_20260608.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260601_vs_20260608.xlsx
@@ -11518,7 +11518,7 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉江夏永旺销售中心</t>
+          <t>小鹏汽车武汉江宸龙湖天街销售中心</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
@@ -11533,12 +11533,12 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>湖北省武汉市江夏区文化大道199号永旺梦乐城1F-1062-2</t>
+          <t>湖北省武汉市江汉区青年路518号江宸龙湖天街负一楼小鹏汽车体验中心</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>连续在档 5 期；本期存在高相似店名「小鹏汽车武汉经开永旺销售中心」（疑似改名/合并，非真实关店）</t>
+          <t>连续在档 5 期</t>
         </is>
       </c>
     </row>
@@ -11550,7 +11550,7 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉江宸龙湖天街销售中心</t>
+          <t>小鹏汽车武汉江夏永旺销售中心</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
@@ -11565,12 +11565,12 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>湖北省武汉市江汉区青年路518号江宸龙湖天街负一楼小鹏汽车体验中心</t>
+          <t>湖北省武汉市江夏区文化大道199号永旺梦乐城1F-1062-2</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>连续在档 5 期</t>
+          <t>连续在档 5 期；本期存在高相似店名「小鹏汽车武汉经开永旺销售中心」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -11582,7 +11582,7 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>小鹏汽车西安芙蓉新天地销售中心</t>
+          <t>小鹏汽车西安王府井销售中心</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
@@ -11597,7 +11597,7 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>西安市曲江新区芙蓉南路芙蓉新天地购物中心1F-F1005</t>
+          <t>陕西省西安市未央区未央路170号熙地港负一层王府井新能源展厅</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
@@ -11614,7 +11614,7 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>小鹏汽车西安王府井销售中心</t>
+          <t>小鹏汽车西安芙蓉新天地销售中心</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -11629,7 +11629,7 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>陕西省西安市未央区未央路170号熙地港负一层王府井新能源展厅</t>
+          <t>西安市曲江新区芙蓉南路芙蓉新天地购物中心1F-F1005</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
@@ -12094,7 +12094,7 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>华为授权体验店（融创广场）</t>
+          <t>华为授权体验店（相城龙湖）</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
@@ -12104,12 +12104,12 @@
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>淮安市</t>
+          <t>苏州市</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 江苏省淮安市清江浦区天津路融创广场一楼华为</t>
+          <t>江苏省苏州市相城区相城大道1399号龙湖天街一层A1F-25、26号</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
@@ -12446,7 +12446,7 @@
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>华为智能生活馆•西宁城东吾悦</t>
+          <t>华为智能生活馆•西宁海湖万达</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
@@ -12461,7 +12461,7 @@
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>青海省西宁市城东区八一路与民和路交叉口东南西宁城东吾悦广场</t>
+          <t>青海省西宁市城西区海湖新区西关大街海湖万达广场2号门左侧</t>
         </is>
       </c>
       <c r="F50" s="3" t="inlineStr">
@@ -12510,7 +12510,7 @@
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>华为智能生活馆•西宁海湖万达</t>
+          <t>华为智能生活馆•西宁城东吾悦</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
@@ -12525,7 +12525,7 @@
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>青海省西宁市城西区海湖新区西关大街海湖万达广场2号门左侧</t>
+          <t>青海省西宁市城东区八一路与民和路交叉口东南西宁城东吾悦广场</t>
         </is>
       </c>
       <c r="F52" s="3" t="inlineStr">
@@ -12596,17 +12596,17 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车乐山天牛汽车城销售服务中心</t>
+          <t>小鹏汽车福州海盛汽车城交付中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车乐山天牛汽车城销售服务中心</t>
+          <t>小鹏汽车福州海盛汽车城交付中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12616,29 +12616,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>四川省乐山市市中区龙游路北段518号 → 四川省乐山市市中区龙游路北段518号1幢</t>
+          <t>福州市闽侯县荆溪镇永丰村洪甘路189号海盛汽车城 → 荆溪镇永丰村杜坞42号海盛汽车城A区5栋1层小鹏福州海盛交付中心</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>上海德辰汽车销售有限公司</t>
+          <t>小鹏汽车重庆万象城销售中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>上海德辰汽车销售有限公司</t>
+          <t>小鹏汽车重庆万象城销售中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12648,7 +12648,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>上海市闵行区颛兴东路1280弄3号(都会路口) → 上海市闵行区莲花南路2333号</t>
+          <t>重庆市九龙坡区万象城北区 → 重庆市九龙坡区万象城北区3号门NL132</t>
         </is>
       </c>
     </row>
@@ -12660,17 +12660,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州海盛汽车城交付中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州海盛汽车城交付中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12680,29 +12680,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>福州市闽侯县荆溪镇永丰村洪甘路189号海盛汽车城 → 荆溪镇永丰村杜坞42号海盛汽车城A区5栋1层小鹏福州海盛交付中心</t>
+          <t>青岛市市北区四流南路22号-8幢展厅 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小米之家湖南省长沙市岳麓区长沙万象城汽车体验店</t>
+          <t>上海德辰汽车销售有限公司</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小米之家湖南省长沙市岳麓区长沙万象城汽车体验店</t>
+          <t>上海德辰汽车销售有限公司</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12712,29 +12712,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>桐兴巷与铜盆湖路交叉口西北160米 → 湖南省长沙市岳麓区桐兴巷与铜盆湖路交叉口西北160米</t>
+          <t>上海市闵行区颛兴东路1280弄3号(都会路口) → 上海市闵行区莲花南路2333号</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>小鹏汽车广州龙溪大道销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>小鹏汽车广州龙溪大道销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12744,7 +12744,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>龙跃街9号院 顺义区马坡聚源工业园 101317 → 新东路幸福二村40号楼 朝阳区 100027</t>
+          <t>广东省广州市荔湾区龙溪大道488号场内自编号为86号 → 广东省广州市荔湾区龙溪大道488号金马汽车交易城小鹏汽车</t>
         </is>
       </c>
     </row>
@@ -12756,17 +12756,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津北辰双江道销售服务中心</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津北辰双江道销售服务中心</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12776,7 +12776,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>天津市北辰区双街镇庞大汽贸园原五菱宝骏店展厅 → 天津市北辰区双街镇庞大汽贸园原五菱骏宝店展厅</t>
+          <t>佛山市禅城区南庄镇醒群社村工业区5号 → 广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号</t>
         </is>
       </c>
     </row>
@@ -12788,17 +12788,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>小鹏汽车深圳福保销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>小鹏汽车深圳福保销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12808,7 +12808,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>河北省张家口市经济技术开发区张宣公路西侧白云街1号 → 河北省张家口市经济技术开发区白云街1号万国汽配城后</t>
+          <t>深圳市福田保税区蓝花道6号诚联物流大厦1层 → 广东省深圳市福田区蓝花道6号城联物流大厦一层</t>
         </is>
       </c>
     </row>
@@ -12820,17 +12820,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车文山国际汽车城销售中心</t>
+          <t>小鹏汽车天津北辰双江道销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车文山国际汽车城销售中心</t>
+          <t>小鹏汽车天津北辰双江道销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12840,29 +12840,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>云南省文山壮族苗族自治州文山市腾龙北路世纪名苑二期 → 云南省文山壮族苗族自治州文山市腾龙北路世纪名苑B期第28-31号商铺</t>
+          <t>天津市北辰区双街镇庞大汽贸园原五菱宝骏店展厅 → 天津市北辰区双街镇庞大汽贸园原五菱骏宝店展厅</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>昆明经开特斯拉中心</t>
+          <t>小鹏汽车海口南海大道销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>昆明经开特斯拉中心</t>
+          <t>小鹏汽车海口南海大道销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12872,7 +12872,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>云南省昆明市自由贸易试验区昆明片区经开区出口加工区A6-1-2号（宝泽路41号）2栋 → 云南省昆明市经济开发区宝泽路41号2栋</t>
+          <t>海南省海口市龙华区南海大道115号福德汽车城小鹏汽车 → 海南省海口市龙华区南海大道115号</t>
         </is>
       </c>
     </row>
@@ -12884,17 +12884,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
+          <t>小鹏汽车北京五方天雅销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
+          <t>小鹏汽车北京五方天雅销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12904,29 +12904,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>四川省遂宁市遂宁高新区物流港物流大道858-888号 → 四川省遂宁市遂宁高新区物流港主干道B南侧858-888号</t>
+          <t>北京市朝阳区王四营乡五方天雅B区B1-03 → 北京市朝阳区五方桥西南侧五方天雅市场内B区B1-03号</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京五方天雅销售服务中心</t>
+          <t>华为授权体验店（东吴银泰）</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京五方天雅销售服务中心</t>
+          <t>华为授权体验店（东吴银泰）</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12936,7 +12936,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>北京市朝阳区王四营乡五方天雅B区B1-03 → 北京市朝阳区五方桥西南侧五方天雅市场内B区B1-03号</t>
+          <t>浙江省湖州市吴兴区劳动路518号湖州东吴银泰城1F层【1001-A,1001-B,1002、1-39】号 → 湖州市吴兴区劳动路518号湖州东吴银泰城1F层C馆（1001-A,1001-B,1002-C) 华为授权体验店</t>
         </is>
       </c>
     </row>
@@ -12948,17 +12948,17 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12968,29 +12968,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>繁华大道29华天大厦向东20米3号整栋标准厂房 → 安徽省合肥市包河经济开发区繁华大道29华天大厦向东20米3号整栋标准厂房</t>
+          <t>新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅 → 新疆伊宁市巴彦岱城投汽车产业园</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小米之家湖南省长沙市岳麓区长沙万象城汽车体验店</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小米之家湖南省长沙市岳麓区长沙万象城汽车体验店</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -13000,29 +13000,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
+          <t>桐兴巷与铜盆湖路交叉口西北160米 → 湖南省长沙市岳麓区桐兴巷与铜盆湖路交叉口西北160米</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>广州市锦龙汽车发展有限公司</t>
+          <t>小鹏汽车潍坊潍州路销售服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>广州市锦龙汽车发展有限公司</t>
+          <t>小鹏汽车潍坊潍州路销售服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -13032,29 +13032,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>广东省广州市天河区广东省广州市天河区黄村街道奥体路55号(奥林匹克体育中心东门对面) → 广东省广州市天河区奥体南路5号</t>
+          <t>山东省潍坊市奎文区潍州路2800号 → 潍坊市奎文区金宝乐园南100米路西</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（东吴银泰）</t>
+          <t>小鹏汽车乐山天牛汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（东吴银泰）</t>
+          <t>小鹏汽车乐山天牛汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -13064,7 +13064,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>浙江省湖州市吴兴区劳动路518号湖州东吴银泰城1F层【1001-A,1001-B,1002、1-39】号 → 湖州市吴兴区劳动路518号湖州东吴银泰城1F层C馆（1001-A,1001-B,1002-C) 华为授权体验店</t>
+          <t>四川省乐山市市中区龙游路北段518号 → 四川省乐山市市中区龙游路北段518号1幢</t>
         </is>
       </c>
     </row>
@@ -13076,17 +13076,17 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13096,29 +13096,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>佛山市禅城区南庄镇醒群社村工业区5号 → 广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号</t>
+          <t>繁华大道29华天大厦向东20米3号整栋标准厂房 → 安徽省合肥市包河经济开发区繁华大道29华天大厦向东20米3号整栋标准厂房</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆万象城销售中心</t>
+          <t>昆明经开特斯拉中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆万象城销售中心</t>
+          <t>昆明经开特斯拉中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13128,7 +13128,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>重庆市九龙坡区万象城北区 → 重庆市九龙坡区万象城北区3号门NL132</t>
+          <t>云南省昆明市自由贸易试验区昆明片区经开区出口加工区A6-1-2号（宝泽路41号）2栋 → 云南省昆明市经济开发区宝泽路41号2栋</t>
         </is>
       </c>
     </row>
@@ -13140,17 +13140,17 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊潍州路销售服务中心</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊潍州路销售服务中心</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13160,14 +13160,14 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>山东省潍坊市奎文区潍州路2800号 → 潍坊市奎文区金宝乐园南100米路西</t>
+          <t>河北省张家口市经济技术开发区张宣公路西侧白云街1号 → 河北省张家口市经济技术开发区白云街1号万国汽配城后</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
@@ -13177,12 +13177,12 @@
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳福保销售服务中心</t>
+          <t>广州市锦龙汽车发展有限公司</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳福保销售服务中心</t>
+          <t>广州市锦龙汽车发展有限公司</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13192,7 +13192,7 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>深圳市福田保税区蓝花道6号诚联物流大厦1层 → 广东省深圳市福田区蓝花道6号城联物流大厦一层</t>
+          <t>广东省广州市天河区广东省广州市天河区黄村街道奥体路55号(奥林匹克体育中心东门对面) → 广东省广州市天河区奥体南路5号</t>
         </is>
       </c>
     </row>
@@ -13204,17 +13204,17 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海口南海大道销售服务中心</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海口南海大道销售服务中心</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13224,29 +13224,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>海南省海口市龙华区南海大道115号福德汽车城小鹏汽车 → 海南省海口市龙华区南海大道115号</t>
+          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13256,7 +13256,7 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅 → 新疆伊宁市巴彦岱城投汽车产业园</t>
+          <t>龙跃街9号院 顺义区马坡聚源工业园 101317 → 新东路幸福二村40号楼 朝阳区 100027</t>
         </is>
       </c>
     </row>
@@ -13300,17 +13300,17 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车文山国际汽车城销售中心</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车文山国际汽车城销售中心</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13320,7 +13320,7 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区四流南路22号-8幢展厅 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心</t>
+          <t>云南省文山壮族苗族自治州文山市腾龙北路世纪名苑二期 → 云南省文山壮族苗族自治州文山市腾龙北路世纪名苑B期第28-31号商铺</t>
         </is>
       </c>
     </row>
@@ -13332,17 +13332,17 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州龙溪大道销售服务中心</t>
+          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州龙溪大道销售服务中心</t>
+          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13352,7 +13352,7 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>广东省广州市荔湾区龙溪大道488号场内自编号为86号 → 广东省广州市荔湾区龙溪大道488号金马汽车交易城小鹏汽车</t>
+          <t>四川省遂宁市遂宁高新区物流港物流大道858-888号 → 四川省遂宁市遂宁高新区物流港主干道B南侧858-888号</t>
         </is>
       </c>
     </row>
@@ -13364,17 +13364,17 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常州金坛汽车城销售中心</t>
+          <t>小鹏汽车保山联通汽车城销售中心</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常州金坛汽车城销售展厅</t>
+          <t>小鹏汽车保山联通汽车城销售展厅</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -13384,7 +13384,7 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常州金坛汽车城销售中心 → 小鹏汽车常州金坛汽车城销售展厅</t>
+          <t>小鹏汽车保山联通汽车城销售中心 → 小鹏汽车保山联通汽车城销售展厅</t>
         </is>
       </c>
     </row>
@@ -13396,17 +13396,17 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保山联通汽车城销售中心</t>
+          <t>小鹏汽车常州金坛汽车城销售中心</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保山联通汽车城销售展厅</t>
+          <t>小鹏汽车常州金坛汽车城销售展厅</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -13416,7 +13416,7 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保山联通汽车城销售中心 → 小鹏汽车保山联通汽车城销售展厅</t>
+          <t>小鹏汽车常州金坛汽车城销售中心 → 小鹏汽车常州金坛汽车城销售展厅</t>
         </is>
       </c>
     </row>
@@ -13460,17 +13460,17 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>上海松江万达</t>
+          <t>深圳光明蓝鲸世界体验店L1-07/08</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>上海松江万达广场</t>
+          <t>深圳光明蓝鲸世界体验店</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -13492,17 +13492,17 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>深圳光明蓝鲸世界体验店L1-07/08</t>
+          <t>上海松江万达</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>深圳光明蓝鲸世界体验店</t>
+          <t>上海松江万达广场</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -13519,22 +13519,22 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>宾利北京亦庄</t>
+          <t>小鹏汽车上海临港万达广场销售中心</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>宾利北京五棵松（新）</t>
+          <t>小鹏汽车上海临港万达销售展厅</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -13583,22 +13583,22 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海临港万达广场销售中心</t>
+          <t>宾利北京亦庄</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海临港万达销售展厅</t>
+          <t>宾利北京五棵松（新）</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -13652,17 +13652,17 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•蚌埠银泰</t>
+          <t>华为授权体验店（融创广场）</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•蚌埠银泰城</t>
+          <t>华为授权体验店（永旺梦乐城）</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -13672,7 +13672,7 @@
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 96%</t>
+          <t>店名相似度 100%</t>
         </is>
       </c>
     </row>
@@ -13684,17 +13684,17 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（相城龙湖）</t>
+          <t>华为智能生活馆•蚌埠银泰</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（永旺梦乐城）</t>
+          <t>华为智能生活馆•蚌埠银泰城</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -13704,7 +13704,7 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 100%</t>
+          <t>店名相似度 96%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260601_vs_20260608.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260601_vs_20260608.xlsx
@@ -11518,7 +11518,7 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉江宸龙湖天街销售中心</t>
+          <t>小鹏汽车武汉江夏永旺销售中心</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
@@ -11533,12 +11533,12 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>湖北省武汉市江汉区青年路518号江宸龙湖天街负一楼小鹏汽车体验中心</t>
+          <t>湖北省武汉市江夏区文化大道199号永旺梦乐城1F-1062-2</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>连续在档 5 期</t>
+          <t>连续在档 5 期；本期存在高相似店名「小鹏汽车武汉经开永旺销售中心」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -11550,7 +11550,7 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉江夏永旺销售中心</t>
+          <t>小鹏汽车武汉江宸龙湖天街销售中心</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
@@ -11565,12 +11565,12 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>湖北省武汉市江夏区文化大道199号永旺梦乐城1F-1062-2</t>
+          <t>湖北省武汉市江汉区青年路518号江宸龙湖天街负一楼小鹏汽车体验中心</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>连续在档 5 期；本期存在高相似店名「小鹏汽车武汉经开永旺销售中心」（疑似改名/合并，非真实关店）</t>
+          <t>连续在档 5 期</t>
         </is>
       </c>
     </row>
@@ -11582,7 +11582,7 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>小鹏汽车西安王府井销售中心</t>
+          <t>小鹏汽车西安芙蓉新天地销售中心</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
@@ -11597,7 +11597,7 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>陕西省西安市未央区未央路170号熙地港负一层王府井新能源展厅</t>
+          <t>西安市曲江新区芙蓉南路芙蓉新天地购物中心1F-F1005</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
@@ -11614,7 +11614,7 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>小鹏汽车西安芙蓉新天地销售中心</t>
+          <t>小鹏汽车西安王府井销售中心</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -11629,7 +11629,7 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>西安市曲江新区芙蓉南路芙蓉新天地购物中心1F-F1005</t>
+          <t>陕西省西安市未央区未央路170号熙地港负一层王府井新能源展厅</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
@@ -12094,7 +12094,7 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>华为授权体验店（相城龙湖）</t>
+          <t>华为授权体验店（融创广场）</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
@@ -12104,12 +12104,12 @@
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>苏州市</t>
+          <t>淮安市</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>江苏省苏州市相城区相城大道1399号龙湖天街一层A1F-25、26号</t>
+          <t xml:space="preserve"> 江苏省淮安市清江浦区天津路融创广场一楼华为</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
@@ -12596,17 +12596,17 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州海盛汽车城交付中心</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州海盛汽车城交付中心</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12616,7 +12616,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>福州市闽侯县荆溪镇永丰村洪甘路189号海盛汽车城 → 荆溪镇永丰村杜坞42号海盛汽车城A区5栋1层小鹏福州海盛交付中心</t>
+          <t>河北省张家口市经济技术开发区张宣公路西侧白云街1号 → 河北省张家口市经济技术开发区白云街1号万国汽配城后</t>
         </is>
       </c>
     </row>
@@ -12628,17 +12628,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆万象城销售中心</t>
+          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆万象城销售中心</t>
+          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12648,29 +12648,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>重庆市九龙坡区万象城北区 → 重庆市九龙坡区万象城北区3号门NL132</t>
+          <t>繁华大道29华天大厦向东20米3号整栋标准厂房 → 安徽省合肥市包河经济开发区繁华大道29华天大厦向东20米3号整栋标准厂房</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>华为授权体验店（东吴银泰）</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>华为授权体验店（东吴银泰）</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12680,29 +12680,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区四流南路22号-8幢展厅 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心</t>
+          <t>浙江省湖州市吴兴区劳动路518号湖州东吴银泰城1F层【1001-A,1001-B,1002、1-39】号 → 湖州市吴兴区劳动路518号湖州东吴银泰城1F层C馆（1001-A,1001-B,1002-C) 华为授权体验店</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>上海德辰汽车销售有限公司</t>
+          <t>小鹏汽车天津北辰双江道销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>上海德辰汽车销售有限公司</t>
+          <t>小鹏汽车天津北辰双江道销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12712,7 +12712,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>上海市闵行区颛兴东路1280弄3号(都会路口) → 上海市闵行区莲花南路2333号</t>
+          <t>天津市北辰区双街镇庞大汽贸园原五菱宝骏店展厅 → 天津市北辰区双街镇庞大汽贸园原五菱骏宝店展厅</t>
         </is>
       </c>
     </row>
@@ -12724,17 +12724,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州龙溪大道销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州龙溪大道销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12744,7 +12744,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>广东省广州市荔湾区龙溪大道488号场内自编号为86号 → 广东省广州市荔湾区龙溪大道488号金马汽车交易城小鹏汽车</t>
+          <t>青岛市市北区四流南路22号-8幢展厅 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心</t>
         </is>
       </c>
     </row>
@@ -12756,17 +12756,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>小鹏汽车文山国际汽车城销售中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>小鹏汽车文山国际汽车城销售中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12776,7 +12776,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>佛山市禅城区南庄镇醒群社村工业区5号 → 广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号</t>
+          <t>云南省文山壮族苗族自治州文山市腾龙北路世纪名苑二期 → 云南省文山壮族苗族自治州文山市腾龙北路世纪名苑B期第28-31号商铺</t>
         </is>
       </c>
     </row>
@@ -12793,12 +12793,12 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳福保销售服务中心</t>
+          <t>小鹏汽车汕头龙湖销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳福保销售服务中心</t>
+          <t>小鹏汽车汕头龙湖销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12808,7 +12808,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>深圳市福田保税区蓝花道6号诚联物流大厦1层 → 广东省深圳市福田区蓝花道6号城联物流大厦一层</t>
+          <t>广东省汕头市龙湖区汕汾路与淮河路交界处北侧 → 汕头市龙湖区汕汾路与淮河路交界处北侧之一（东侧）</t>
         </is>
       </c>
     </row>
@@ -12820,17 +12820,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津北辰双江道销售服务中心</t>
+          <t>小鹏汽车海口南海大道销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津北辰双江道销售服务中心</t>
+          <t>小鹏汽车海口南海大道销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12840,7 +12840,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>天津市北辰区双街镇庞大汽贸园原五菱宝骏店展厅 → 天津市北辰区双街镇庞大汽贸园原五菱骏宝店展厅</t>
+          <t>海南省海口市龙华区南海大道115号福德汽车城小鹏汽车 → 海南省海口市龙华区南海大道115号</t>
         </is>
       </c>
     </row>
@@ -12852,17 +12852,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海口南海大道销售服务中心</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海口南海大道销售服务中心</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12872,7 +12872,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>海南省海口市龙华区南海大道115号福德汽车城小鹏汽车 → 海南省海口市龙华区南海大道115号</t>
+          <t>新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅 → 新疆伊宁市巴彦岱城投汽车产业园</t>
         </is>
       </c>
     </row>
@@ -12884,17 +12884,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京五方天雅销售服务中心</t>
+          <t>小鹏汽车乐山天牛汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京五方天雅销售服务中心</t>
+          <t>小鹏汽车乐山天牛汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12904,29 +12904,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>北京市朝阳区王四营乡五方天雅B区B1-03 → 北京市朝阳区五方桥西南侧五方天雅市场内B区B1-03号</t>
+          <t>四川省乐山市市中区龙游路北段518号 → 四川省乐山市市中区龙游路北段518号1幢</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（东吴银泰）</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（东吴银泰）</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12936,29 +12936,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>浙江省湖州市吴兴区劳动路518号湖州东吴银泰城1F层【1001-A,1001-B,1002、1-39】号 → 湖州市吴兴区劳动路518号湖州东吴银泰城1F层C馆（1001-A,1001-B,1002-C) 华为授权体验店</t>
+          <t>龙跃街9号院 顺义区马坡聚源工业园 101317 → 新东路幸福二村40号楼 朝阳区 100027</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>上海德辰汽车销售有限公司</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>上海德辰汽车销售有限公司</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12968,29 +12968,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅 → 新疆伊宁市巴彦岱城投汽车产业园</t>
+          <t>上海市闵行区颛兴东路1280弄3号(都会路口) → 上海市闵行区莲花南路2333号</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小米之家湖南省长沙市岳麓区长沙万象城汽车体验店</t>
+          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小米之家湖南省长沙市岳麓区长沙万象城汽车体验店</t>
+          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -13000,7 +13000,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>桐兴巷与铜盆湖路交叉口西北160米 → 湖南省长沙市岳麓区桐兴巷与铜盆湖路交叉口西北160米</t>
+          <t>四川省遂宁市遂宁高新区物流港物流大道858-888号 → 四川省遂宁市遂宁高新区物流港主干道B南侧858-888号</t>
         </is>
       </c>
     </row>
@@ -13012,17 +13012,17 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊潍州路销售服务中心</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊潍州路销售服务中心</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -13032,7 +13032,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>山东省潍坊市奎文区潍州路2800号 → 潍坊市奎文区金宝乐园南100米路西</t>
+          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
         </is>
       </c>
     </row>
@@ -13044,17 +13044,17 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车乐山天牛汽车城销售服务中心</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车乐山天牛汽车城销售服务中心</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -13064,7 +13064,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>四川省乐山市市中区龙游路北段518号 → 四川省乐山市市中区龙游路北段518号1幢</t>
+          <t>佛山市禅城区南庄镇醒群社村工业区5号 → 广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号</t>
         </is>
       </c>
     </row>
@@ -13076,17 +13076,17 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
+          <t>小鹏汽车福州海盛汽车城交付中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
+          <t>小鹏汽车福州海盛汽车城交付中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13096,29 +13096,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>繁华大道29华天大厦向东20米3号整栋标准厂房 → 安徽省合肥市包河经济开发区繁华大道29华天大厦向东20米3号整栋标准厂房</t>
+          <t>福州市闽侯县荆溪镇永丰村洪甘路189号海盛汽车城 → 荆溪镇永丰村杜坞42号海盛汽车城A区5栋1层小鹏福州海盛交付中心</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>昆明经开特斯拉中心</t>
+          <t>小鹏汽车广州龙溪大道销售服务中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>昆明经开特斯拉中心</t>
+          <t>小鹏汽车广州龙溪大道销售服务中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13128,7 +13128,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>云南省昆明市自由贸易试验区昆明片区经开区出口加工区A6-1-2号（宝泽路41号）2栋 → 云南省昆明市经济开发区宝泽路41号2栋</t>
+          <t>广东省广州市荔湾区龙溪大道488号场内自编号为86号 → 广东省广州市荔湾区龙溪大道488号金马汽车交易城小鹏汽车</t>
         </is>
       </c>
     </row>
@@ -13140,17 +13140,17 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>小鹏汽车北京五方天雅销售服务中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>小鹏汽车北京五方天雅销售服务中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13160,29 +13160,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>河北省张家口市经济技术开发区张宣公路西侧白云街1号 → 河北省张家口市经济技术开发区白云街1号万国汽配城后</t>
+          <t>北京市朝阳区王四营乡五方天雅B区B1-03 → 北京市朝阳区五方桥西南侧五方天雅市场内B区B1-03号</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>广州市锦龙汽车发展有限公司</t>
+          <t>小鹏汽车潍坊潍州路销售服务中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>广州市锦龙汽车发展有限公司</t>
+          <t>小鹏汽车潍坊潍州路销售服务中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13192,29 +13192,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>广东省广州市天河区广东省广州市天河区黄村街道奥体路55号(奥林匹克体育中心东门对面) → 广东省广州市天河区奥体南路5号</t>
+          <t>山东省潍坊市奎文区潍州路2800号 → 潍坊市奎文区金宝乐园南100米路西</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>广州市锦龙汽车发展有限公司</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>广州市锦龙汽车发展有限公司</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13224,29 +13224,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
+          <t>广东省广州市天河区广东省广州市天河区黄村街道奥体路55号(奥林匹克体育中心东门对面) → 广东省广州市天河区奥体南路5号</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>昆明经开特斯拉中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>昆明经开特斯拉中心</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13256,29 +13256,29 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>龙跃街9号院 顺义区马坡聚源工业园 101317 → 新东路幸福二村40号楼 朝阳区 100027</t>
+          <t>云南省昆明市自由贸易试验区昆明片区经开区出口加工区A6-1-2号（宝泽路41号）2栋 → 云南省昆明市经济开发区宝泽路41号2栋</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕头龙湖销售服务中心</t>
+          <t>小米之家湖南省长沙市岳麓区长沙万象城汽车体验店</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕头龙湖销售服务中心</t>
+          <t>小米之家湖南省长沙市岳麓区长沙万象城汽车体验店</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13288,7 +13288,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>广东省汕头市龙湖区汕汾路与淮河路交界处北侧 → 汕头市龙湖区汕汾路与淮河路交界处北侧之一（东侧）</t>
+          <t>桐兴巷与铜盆湖路交叉口西北160米 → 湖南省长沙市岳麓区桐兴巷与铜盆湖路交叉口西北160米</t>
         </is>
       </c>
     </row>
@@ -13300,17 +13300,17 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车文山国际汽车城销售中心</t>
+          <t>小鹏汽车深圳福保销售服务中心</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车文山国际汽车城销售中心</t>
+          <t>小鹏汽车深圳福保销售服务中心</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13320,7 +13320,7 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>云南省文山壮族苗族自治州文山市腾龙北路世纪名苑二期 → 云南省文山壮族苗族自治州文山市腾龙北路世纪名苑B期第28-31号商铺</t>
+          <t>深圳市福田保税区蓝花道6号诚联物流大厦1层 → 广东省深圳市福田区蓝花道6号城联物流大厦一层</t>
         </is>
       </c>
     </row>
@@ -13332,17 +13332,17 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
+          <t>小鹏汽车重庆万象城销售中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
+          <t>小鹏汽车重庆万象城销售中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13352,7 +13352,7 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>四川省遂宁市遂宁高新区物流港物流大道858-888号 → 四川省遂宁市遂宁高新区物流港主干道B南侧858-888号</t>
+          <t>重庆市九龙坡区万象城北区 → 重庆市九龙坡区万象城北区3号门NL132</t>
         </is>
       </c>
     </row>
@@ -13364,17 +13364,17 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保山联通汽车城销售中心</t>
+          <t>小鹏汽车常州金坛汽车城销售中心</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保山联通汽车城销售展厅</t>
+          <t>小鹏汽车常州金坛汽车城销售展厅</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -13384,7 +13384,7 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保山联通汽车城销售中心 → 小鹏汽车保山联通汽车城销售展厅</t>
+          <t>小鹏汽车常州金坛汽车城销售中心 → 小鹏汽车常州金坛汽车城销售展厅</t>
         </is>
       </c>
     </row>
@@ -13396,17 +13396,17 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常州金坛汽车城销售中心</t>
+          <t>小鹏汽车保山联通汽车城销售中心</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常州金坛汽车城销售展厅</t>
+          <t>小鹏汽车保山联通汽车城销售展厅</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -13416,29 +13416,29 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常州金坛汽车城销售中心 → 小鹏汽车常州金坛汽车城销售展厅</t>
+          <t>小鹏汽车保山联通汽车城销售中心 → 小鹏汽车保山联通汽车城销售展厅</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•佛山岭南新天地</t>
+          <t>宾利北京亦庄</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•佛山岭南天地</t>
+          <t>宾利北京五棵松（新）</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -13455,7 +13455,7 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
@@ -13465,12 +13465,12 @@
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>深圳光明蓝鲸世界体验店L1-07/08</t>
+          <t>华为智能生活馆•佛山岭南新天地</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>深圳光明蓝鲸世界体验店</t>
+          <t>华为智能生活馆•佛山岭南天地</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -13519,22 +13519,22 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海临港万达广场销售中心</t>
+          <t>宾利北京亦庄</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海临港万达销售展厅</t>
+          <t>宾利北京五棵松（新）</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -13551,22 +13551,22 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>宾利北京亦庄</t>
+          <t>小鹏汽车上海临港万达广场销售中心</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>宾利北京五棵松（新）</t>
+          <t>小鹏汽车上海临港万达销售展厅</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -13583,22 +13583,22 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>宾利北京亦庄</t>
+          <t>深圳光明蓝鲸世界体验店L1-07/08</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>宾利北京五棵松（新）</t>
+          <t>深圳光明蓝鲸世界体验店</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -13652,17 +13652,17 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（融创广场）</t>
+          <t>华为智能生活馆•蚌埠银泰</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（永旺梦乐城）</t>
+          <t>华为智能生活馆•蚌埠银泰城</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -13672,7 +13672,7 @@
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 100%</t>
+          <t>店名相似度 96%</t>
         </is>
       </c>
     </row>
@@ -13684,17 +13684,17 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•蚌埠银泰</t>
+          <t>华为授权体验店（相城龙湖）</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•蚌埠银泰城</t>
+          <t>华为授权体验店（永旺梦乐城）</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -13704,7 +13704,7 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 96%</t>
+          <t>店名相似度 100%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260601_vs_20260608.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260601_vs_20260608.xlsx
@@ -11518,7 +11518,7 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉江夏永旺销售中心</t>
+          <t>小鹏汽车武汉江宸龙湖天街销售中心</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
@@ -11533,12 +11533,12 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>湖北省武汉市江夏区文化大道199号永旺梦乐城1F-1062-2</t>
+          <t>湖北省武汉市江汉区青年路518号江宸龙湖天街负一楼小鹏汽车体验中心</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>连续在档 5 期；本期存在高相似店名「小鹏汽车武汉经开永旺销售中心」（疑似改名/合并，非真实关店）</t>
+          <t>连续在档 5 期</t>
         </is>
       </c>
     </row>
@@ -11550,7 +11550,7 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉江宸龙湖天街销售中心</t>
+          <t>小鹏汽车武汉江夏永旺销售中心</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
@@ -11565,12 +11565,12 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>湖北省武汉市江汉区青年路518号江宸龙湖天街负一楼小鹏汽车体验中心</t>
+          <t>湖北省武汉市江夏区文化大道199号永旺梦乐城1F-1062-2</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>连续在档 5 期</t>
+          <t>连续在档 5 期；本期存在高相似店名「小鹏汽车武汉经开永旺销售中心」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -12478,7 +12478,7 @@
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>华为智能生活馆•西宁王府井百货</t>
+          <t>华为智能生活馆•西宁城东吾悦</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
@@ -12493,7 +12493,7 @@
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>青海省西宁市城中区西大街王府井百货B馆</t>
+          <t>青海省西宁市城东区八一路与民和路交叉口东南西宁城东吾悦广场</t>
         </is>
       </c>
       <c r="F51" s="3" t="inlineStr">
@@ -12510,7 +12510,7 @@
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>华为智能生活馆•西宁城东吾悦</t>
+          <t>华为智能生活馆•西宁王府井百货</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
@@ -12525,7 +12525,7 @@
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>青海省西宁市城东区八一路与民和路交叉口东南西宁城东吾悦广场</t>
+          <t>青海省西宁市城中区西大街王府井百货B馆</t>
         </is>
       </c>
       <c r="F52" s="3" t="inlineStr">
@@ -12623,22 +12623,22 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
+          <t>小米之家湖南省长沙市岳麓区长沙万象城汽车体验店</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
+          <t>小米之家湖南省长沙市岳麓区长沙万象城汽车体验店</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12648,29 +12648,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>繁华大道29华天大厦向东20米3号整栋标准厂房 → 安徽省合肥市包河经济开发区繁华大道29华天大厦向东20米3号整栋标准厂房</t>
+          <t>桐兴巷与铜盆湖路交叉口西北160米 → 湖南省长沙市岳麓区桐兴巷与铜盆湖路交叉口西北160米</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（东吴银泰）</t>
+          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（东吴银泰）</t>
+          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12680,7 +12680,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>浙江省湖州市吴兴区劳动路518号湖州东吴银泰城1F层【1001-A,1001-B,1002、1-39】号 → 湖州市吴兴区劳动路518号湖州东吴银泰城1F层C馆（1001-A,1001-B,1002-C) 华为授权体验店</t>
+          <t>繁华大道29华天大厦向东20米3号整栋标准厂房 → 安徽省合肥市包河经济开发区繁华大道29华天大厦向东20米3号整栋标准厂房</t>
         </is>
       </c>
     </row>
@@ -12692,17 +12692,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津北辰双江道销售服务中心</t>
+          <t>小鹏汽车文山国际汽车城销售中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津北辰双江道销售服务中心</t>
+          <t>小鹏汽车文山国际汽车城销售中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12712,7 +12712,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>天津市北辰区双街镇庞大汽贸园原五菱宝骏店展厅 → 天津市北辰区双街镇庞大汽贸园原五菱骏宝店展厅</t>
+          <t>云南省文山壮族苗族自治州文山市腾龙北路世纪名苑二期 → 云南省文山壮族苗族自治州文山市腾龙北路世纪名苑B期第28-31号商铺</t>
         </is>
       </c>
     </row>
@@ -12724,17 +12724,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车汕头龙湖销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车汕头龙湖销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12744,14 +12744,14 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区四流南路22号-8幢展厅 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心</t>
+          <t>广东省汕头市龙湖区汕汾路与淮河路交界处北侧 → 汕头市龙湖区汕汾路与淮河路交界处北侧之一（东侧）</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
@@ -12761,12 +12761,12 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车文山国际汽车城销售中心</t>
+          <t>昆明经开特斯拉中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车文山国际汽车城销售中心</t>
+          <t>昆明经开特斯拉中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12776,7 +12776,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>云南省文山壮族苗族自治州文山市腾龙北路世纪名苑二期 → 云南省文山壮族苗族自治州文山市腾龙北路世纪名苑B期第28-31号商铺</t>
+          <t>云南省昆明市自由贸易试验区昆明片区经开区出口加工区A6-1-2号（宝泽路41号）2栋 → 云南省昆明市经济开发区宝泽路41号2栋</t>
         </is>
       </c>
     </row>
@@ -12788,17 +12788,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕头龙湖销售服务中心</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕头龙湖销售服务中心</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12808,29 +12808,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>广东省汕头市龙湖区汕汾路与淮河路交界处北侧 → 汕头市龙湖区汕汾路与淮河路交界处北侧之一（东侧）</t>
+          <t>新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅 → 新疆伊宁市巴彦岱城投汽车产业园</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海口南海大道销售服务中心</t>
+          <t>广州市锦龙汽车发展有限公司</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海口南海大道销售服务中心</t>
+          <t>广州市锦龙汽车发展有限公司</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12840,7 +12840,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>海南省海口市龙华区南海大道115号福德汽车城小鹏汽车 → 海南省海口市龙华区南海大道115号</t>
+          <t>广东省广州市天河区广东省广州市天河区黄村街道奥体路55号(奥林匹克体育中心东门对面) → 广东省广州市天河区奥体南路5号</t>
         </is>
       </c>
     </row>
@@ -12852,17 +12852,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>小鹏汽车天津北辰双江道销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>小鹏汽车天津北辰双江道销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12872,29 +12872,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅 → 新疆伊宁市巴彦岱城投汽车产业园</t>
+          <t>天津市北辰区双街镇庞大汽贸园原五菱宝骏店展厅 → 天津市北辰区双街镇庞大汽贸园原五菱骏宝店展厅</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车乐山天牛汽车城销售服务中心</t>
+          <t>华为授权体验店（东吴银泰）</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车乐山天牛汽车城销售服务中心</t>
+          <t>华为授权体验店（东吴银泰）</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12904,29 +12904,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>四川省乐山市市中区龙游路北段518号 → 四川省乐山市市中区龙游路北段518号1幢</t>
+          <t>浙江省湖州市吴兴区劳动路518号湖州东吴银泰城1F层【1001-A,1001-B,1002、1-39】号 → 湖州市吴兴区劳动路518号湖州东吴银泰城1F层C馆（1001-A,1001-B,1002-C) 华为授权体验店</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>小鹏汽车乐山天牛汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>小鹏汽车乐山天牛汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12936,29 +12936,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>龙跃街9号院 顺义区马坡聚源工业园 101317 → 新东路幸福二村40号楼 朝阳区 100027</t>
+          <t>四川省乐山市市中区龙游路北段518号 → 四川省乐山市市中区龙游路北段518号1幢</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>上海德辰汽车销售有限公司</t>
+          <t>小鹏汽车福州海盛汽车城交付中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>上海德辰汽车销售有限公司</t>
+          <t>小鹏汽车福州海盛汽车城交付中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12968,7 +12968,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>上海市闵行区颛兴东路1280弄3号(都会路口) → 上海市闵行区莲花南路2333号</t>
+          <t>福州市闽侯县荆溪镇永丰村洪甘路189号海盛汽车城 → 荆溪镇永丰村杜坞42号海盛汽车城A区5栋1层小鹏福州海盛交付中心</t>
         </is>
       </c>
     </row>
@@ -12980,17 +12980,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
+          <t>小鹏汽车重庆万象城销售中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
+          <t>小鹏汽车重庆万象城销售中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -13000,7 +13000,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>四川省遂宁市遂宁高新区物流港物流大道858-888号 → 四川省遂宁市遂宁高新区物流港主干道B南侧858-888号</t>
+          <t>重庆市九龙坡区万象城北区 → 重庆市九龙坡区万象城北区3号门NL132</t>
         </is>
       </c>
     </row>
@@ -13012,17 +13012,17 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小鹏汽车海口南海大道销售服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小鹏汽车海口南海大道销售服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -13032,7 +13032,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
+          <t>海南省海口市龙华区南海大道115号福德汽车城小鹏汽车 → 海南省海口市龙华区南海大道115号</t>
         </is>
       </c>
     </row>
@@ -13049,12 +13049,12 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>小鹏汽车广州龙溪大道销售服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>小鹏汽车广州龙溪大道销售服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -13064,29 +13064,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>佛山市禅城区南庄镇醒群社村工业区5号 → 广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号</t>
+          <t>广东省广州市荔湾区龙溪大道488号场内自编号为86号 → 广东省广州市荔湾区龙溪大道488号金马汽车交易城小鹏汽车</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州海盛汽车城交付中心</t>
+          <t>上海德辰汽车销售有限公司</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州海盛汽车城交付中心</t>
+          <t>上海德辰汽车销售有限公司</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13096,29 +13096,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>福州市闽侯县荆溪镇永丰村洪甘路189号海盛汽车城 → 荆溪镇永丰村杜坞42号海盛汽车城A区5栋1层小鹏福州海盛交付中心</t>
+          <t>上海市闵行区颛兴东路1280弄3号(都会路口) → 上海市闵行区莲花南路2333号</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州龙溪大道销售服务中心</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州龙溪大道销售服务中心</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13128,7 +13128,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>广东省广州市荔湾区龙溪大道488号场内自编号为86号 → 广东省广州市荔湾区龙溪大道488号金马汽车交易城小鹏汽车</t>
+          <t>龙跃街9号院 顺义区马坡聚源工业园 101317 → 新东路幸福二村40号楼 朝阳区 100027</t>
         </is>
       </c>
     </row>
@@ -13140,17 +13140,17 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京五方天雅销售服务中心</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京五方天雅销售服务中心</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13160,7 +13160,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>北京市朝阳区王四营乡五方天雅B区B1-03 → 北京市朝阳区五方桥西南侧五方天雅市场内B区B1-03号</t>
+          <t>佛山市禅城区南庄镇醒群社村工业区5号 → 广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号</t>
         </is>
       </c>
     </row>
@@ -13172,17 +13172,17 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊潍州路销售服务中心</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊潍州路销售服务中心</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13192,29 +13192,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>山东省潍坊市奎文区潍州路2800号 → 潍坊市奎文区金宝乐园南100米路西</t>
+          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>广州市锦龙汽车发展有限公司</t>
+          <t>小鹏汽车北京五方天雅销售服务中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>广州市锦龙汽车发展有限公司</t>
+          <t>小鹏汽车北京五方天雅销售服务中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13224,29 +13224,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>广东省广州市天河区广东省广州市天河区黄村街道奥体路55号(奥林匹克体育中心东门对面) → 广东省广州市天河区奥体南路5号</t>
+          <t>北京市朝阳区王四营乡五方天雅B区B1-03 → 北京市朝阳区五方桥西南侧五方天雅市场内B区B1-03号</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>昆明经开特斯拉中心</t>
+          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>昆明经开特斯拉中心</t>
+          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13256,29 +13256,29 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>云南省昆明市自由贸易试验区昆明片区经开区出口加工区A6-1-2号（宝泽路41号）2栋 → 云南省昆明市经济开发区宝泽路41号2栋</t>
+          <t>四川省遂宁市遂宁高新区物流港物流大道858-888号 → 四川省遂宁市遂宁高新区物流港主干道B南侧858-888号</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小米之家湖南省长沙市岳麓区长沙万象城汽车体验店</t>
+          <t>小鹏汽车潍坊潍州路销售服务中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小米之家湖南省长沙市岳麓区长沙万象城汽车体验店</t>
+          <t>小鹏汽车潍坊潍州路销售服务中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13288,7 +13288,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>桐兴巷与铜盆湖路交叉口西北160米 → 湖南省长沙市岳麓区桐兴巷与铜盆湖路交叉口西北160米</t>
+          <t>山东省潍坊市奎文区潍州路2800号 → 潍坊市奎文区金宝乐园南100米路西</t>
         </is>
       </c>
     </row>
@@ -13300,17 +13300,17 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳福保销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳福保销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13320,7 +13320,7 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>深圳市福田保税区蓝花道6号诚联物流大厦1层 → 广东省深圳市福田区蓝花道6号城联物流大厦一层</t>
+          <t>青岛市市北区四流南路22号-8幢展厅 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心</t>
         </is>
       </c>
     </row>
@@ -13332,17 +13332,17 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆万象城销售中心</t>
+          <t>小鹏汽车深圳福保销售服务中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆万象城销售中心</t>
+          <t>小鹏汽车深圳福保销售服务中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13352,7 +13352,7 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>重庆市九龙坡区万象城北区 → 重庆市九龙坡区万象城北区3号门NL132</t>
+          <t>深圳市福田保税区蓝花道6号诚联物流大厦1层 → 广东省深圳市福田区蓝花道6号城联物流大厦一层</t>
         </is>
       </c>
     </row>
@@ -13364,17 +13364,17 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常州金坛汽车城销售中心</t>
+          <t>小鹏汽车保山联通汽车城销售中心</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常州金坛汽车城销售展厅</t>
+          <t>小鹏汽车保山联通汽车城销售展厅</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -13384,7 +13384,7 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常州金坛汽车城销售中心 → 小鹏汽车常州金坛汽车城销售展厅</t>
+          <t>小鹏汽车保山联通汽车城销售中心 → 小鹏汽车保山联通汽车城销售展厅</t>
         </is>
       </c>
     </row>
@@ -13396,17 +13396,17 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保山联通汽车城销售中心</t>
+          <t>小鹏汽车常州金坛汽车城销售中心</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保山联通汽车城销售展厅</t>
+          <t>小鹏汽车常州金坛汽车城销售展厅</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -13416,7 +13416,7 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保山联通汽车城销售中心 → 小鹏汽车保山联通汽车城销售展厅</t>
+          <t>小鹏汽车常州金坛汽车城销售中心 → 小鹏汽车常州金坛汽车城销售展厅</t>
         </is>
       </c>
     </row>
@@ -13455,7 +13455,7 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
@@ -13465,12 +13465,12 @@
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•佛山岭南新天地</t>
+          <t>深圳光明蓝鲸世界体验店L1-07/08</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•佛山岭南天地</t>
+          <t>深圳光明蓝鲸世界体验店</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -13487,22 +13487,22 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>上海松江万达</t>
+          <t>宾利北京亦庄</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>上海松江万达广场</t>
+          <t>宾利北京五棵松（新）</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -13519,22 +13519,22 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>宾利北京亦庄</t>
+          <t>华为智能生活馆•佛山岭南新天地</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>宾利北京五棵松（新）</t>
+          <t>华为智能生活馆•佛山岭南天地</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -13551,7 +13551,7 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
@@ -13561,12 +13561,12 @@
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海临港万达广场销售中心</t>
+          <t>上海松江万达</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海临港万达销售展厅</t>
+          <t>上海松江万达广场</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -13583,22 +13583,22 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>深圳光明蓝鲸世界体验店L1-07/08</t>
+          <t>小鹏汽车上海临港万达广场销售中心</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>深圳光明蓝鲸世界体验店</t>
+          <t>小鹏汽车上海临港万达销售展厅</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
